--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SAN</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>77501600</v>
+        <v>114524700</v>
       </c>
       <c r="E8" s="3">
-        <v>50412400</v>
+        <v>77723000</v>
       </c>
       <c r="F8" s="3">
-        <v>49629000</v>
+        <v>50556400</v>
       </c>
       <c r="G8" s="3">
-        <v>61611700</v>
+        <v>49770800</v>
       </c>
       <c r="H8" s="3">
-        <v>58942600</v>
+        <v>61787800</v>
       </c>
       <c r="I8" s="3">
-        <v>60804500</v>
+        <v>59111000</v>
       </c>
       <c r="J8" s="3">
+        <v>60978200</v>
+      </c>
+      <c r="K8" s="3">
         <v>59844300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>58387700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>62397900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>61540900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>56488800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71154000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,51 +1005,57 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-3238700</v>
+        <v>-3464500</v>
       </c>
       <c r="E15" s="3">
-        <v>-2990300</v>
+        <v>-3248000</v>
       </c>
       <c r="F15" s="3">
-        <v>-3048900</v>
+        <v>-2998800</v>
       </c>
       <c r="G15" s="3">
-        <v>-3256100</v>
+        <v>-3057600</v>
       </c>
       <c r="H15" s="3">
-        <v>-2631100</v>
+        <v>-3265400</v>
       </c>
       <c r="I15" s="3">
-        <v>-2813400</v>
+        <v>-2638600</v>
       </c>
       <c r="J15" s="3">
+        <v>-2821400</v>
+      </c>
+      <c r="K15" s="3">
         <v>-2564900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-2468300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2637800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2860100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-2625300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2462700</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>47378700</v>
+        <v>81502000</v>
       </c>
       <c r="E17" s="3">
-        <v>22221900</v>
+        <v>47514100</v>
       </c>
       <c r="F17" s="3">
-        <v>28329400</v>
+        <v>22285400</v>
       </c>
       <c r="G17" s="3">
-        <v>33463600</v>
+        <v>28410300</v>
       </c>
       <c r="H17" s="3">
-        <v>31431400</v>
+        <v>33559200</v>
       </c>
       <c r="I17" s="3">
-        <v>33619800</v>
+        <v>31521200</v>
       </c>
       <c r="J17" s="3">
+        <v>33715900</v>
+      </c>
+      <c r="K17" s="3">
         <v>36482000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>35299300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37723700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>43658900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40074800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>48114500</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>30122900</v>
+        <v>33022700</v>
       </c>
       <c r="E18" s="3">
-        <v>28190500</v>
+        <v>30208900</v>
       </c>
       <c r="F18" s="3">
-        <v>21299600</v>
+        <v>28271000</v>
       </c>
       <c r="G18" s="3">
-        <v>28148200</v>
+        <v>21360500</v>
       </c>
       <c r="H18" s="3">
-        <v>27511300</v>
+        <v>28228600</v>
       </c>
       <c r="I18" s="3">
-        <v>27184700</v>
+        <v>27589900</v>
       </c>
       <c r="J18" s="3">
+        <v>27262300</v>
+      </c>
+      <c r="K18" s="3">
         <v>23362200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23088500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>24674200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17882000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16414000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23039500</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-13576600</v>
+        <v>-15113700</v>
       </c>
       <c r="E20" s="3">
-        <v>-12407000</v>
+        <v>-13615400</v>
       </c>
       <c r="F20" s="3">
-        <v>-23552100</v>
+        <v>-12442400</v>
       </c>
       <c r="G20" s="3">
-        <v>-14539000</v>
+        <v>-23619400</v>
       </c>
       <c r="H20" s="3">
-        <v>-12103200</v>
+        <v>-14580500</v>
       </c>
       <c r="I20" s="3">
-        <v>-14065900</v>
+        <v>-12137800</v>
       </c>
       <c r="J20" s="3">
+        <v>-14106100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-11678900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13342900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14259300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9056400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8313000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13815700</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>19783800</v>
+        <v>21394200</v>
       </c>
       <c r="E21" s="3">
-        <v>18772700</v>
+        <v>19860900</v>
       </c>
       <c r="F21" s="3">
-        <v>795300</v>
+        <v>18845300</v>
       </c>
       <c r="G21" s="3">
-        <v>16864000</v>
+        <v>816900</v>
       </c>
       <c r="H21" s="3">
-        <v>18038200</v>
+        <v>16932900</v>
       </c>
       <c r="I21" s="3">
-        <v>15931100</v>
+        <v>18106500</v>
       </c>
       <c r="J21" s="3">
+        <v>15994500</v>
+      </c>
+      <c r="K21" s="3">
         <v>14247300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12166200</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>11674000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>11688100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>16546300</v>
+        <v>17909000</v>
       </c>
       <c r="E23" s="3">
-        <v>15783500</v>
+        <v>16593500</v>
       </c>
       <c r="F23" s="3">
-        <v>-2252500</v>
+        <v>15828600</v>
       </c>
       <c r="G23" s="3">
-        <v>13609200</v>
+        <v>-2258900</v>
       </c>
       <c r="H23" s="3">
-        <v>15408100</v>
+        <v>13648000</v>
       </c>
       <c r="I23" s="3">
-        <v>13118700</v>
+        <v>15452100</v>
       </c>
       <c r="J23" s="3">
+        <v>13156200</v>
+      </c>
+      <c r="K23" s="3">
         <v>11683300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9745600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10414900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8825600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8101000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9223800</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4867300</v>
+        <v>4652700</v>
       </c>
       <c r="E24" s="3">
-        <v>5310000</v>
+        <v>4881200</v>
       </c>
       <c r="F24" s="3">
-        <v>6110700</v>
+        <v>5325200</v>
       </c>
       <c r="G24" s="3">
-        <v>4803300</v>
+        <v>6128200</v>
       </c>
       <c r="H24" s="3">
-        <v>5301300</v>
+        <v>4817000</v>
       </c>
       <c r="I24" s="3">
-        <v>4214100</v>
+        <v>5316500</v>
       </c>
       <c r="J24" s="3">
+        <v>4226200</v>
+      </c>
+      <c r="K24" s="3">
         <v>3561000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2259000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2414200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2433100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2233300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2060000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>11678900</v>
+        <v>13256300</v>
       </c>
       <c r="E26" s="3">
-        <v>10473500</v>
+        <v>11712300</v>
       </c>
       <c r="F26" s="3">
-        <v>-8363200</v>
+        <v>10503400</v>
       </c>
       <c r="G26" s="3">
-        <v>8805900</v>
+        <v>-8387100</v>
       </c>
       <c r="H26" s="3">
-        <v>10106800</v>
+        <v>8831000</v>
       </c>
       <c r="I26" s="3">
-        <v>8904600</v>
+        <v>10135700</v>
       </c>
       <c r="J26" s="3">
+        <v>8930000</v>
+      </c>
+      <c r="K26" s="3">
         <v>8122300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7486500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8000700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6392500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5867700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7163800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>10421400</v>
+        <v>12051800</v>
       </c>
       <c r="E27" s="3">
-        <v>8814500</v>
+        <v>10451200</v>
       </c>
       <c r="F27" s="3">
-        <v>-9516500</v>
+        <v>8839700</v>
       </c>
       <c r="G27" s="3">
-        <v>7068800</v>
+        <v>-9543700</v>
       </c>
       <c r="H27" s="3">
-        <v>8473900</v>
+        <v>7089000</v>
       </c>
       <c r="I27" s="3">
-        <v>7181600</v>
+        <v>8498100</v>
       </c>
       <c r="J27" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="K27" s="3">
         <v>6731300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5808400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6207300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5012100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6238800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1557,17 +1617,20 @@
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>-17900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-16500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>17600</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>13576600</v>
+        <v>15113700</v>
       </c>
       <c r="E32" s="3">
-        <v>12407000</v>
+        <v>13615400</v>
       </c>
       <c r="F32" s="3">
-        <v>23552100</v>
+        <v>12442400</v>
       </c>
       <c r="G32" s="3">
-        <v>14539000</v>
+        <v>23619400</v>
       </c>
       <c r="H32" s="3">
-        <v>12103200</v>
+        <v>14580500</v>
       </c>
       <c r="I32" s="3">
-        <v>14065900</v>
+        <v>12137800</v>
       </c>
       <c r="J32" s="3">
+        <v>14106100</v>
+      </c>
+      <c r="K32" s="3">
         <v>11678900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13342900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14259300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9056400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8313000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13815700</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>10421400</v>
+        <v>12051800</v>
       </c>
       <c r="E33" s="3">
-        <v>8814500</v>
+        <v>10451200</v>
       </c>
       <c r="F33" s="3">
-        <v>-9516500</v>
+        <v>8839700</v>
       </c>
       <c r="G33" s="3">
-        <v>7068800</v>
+        <v>-9543700</v>
       </c>
       <c r="H33" s="3">
-        <v>8473900</v>
+        <v>7089000</v>
       </c>
       <c r="I33" s="3">
-        <v>7181600</v>
+        <v>8498100</v>
       </c>
       <c r="J33" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="K33" s="3">
         <v>6731300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5808400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6207300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4994100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4584200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6256400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>10421400</v>
+        <v>12051800</v>
       </c>
       <c r="E35" s="3">
-        <v>8814500</v>
+        <v>10451200</v>
       </c>
       <c r="F35" s="3">
-        <v>-9516500</v>
+        <v>8839700</v>
       </c>
       <c r="G35" s="3">
-        <v>7068800</v>
+        <v>-9543700</v>
       </c>
       <c r="H35" s="3">
-        <v>8473900</v>
+        <v>7089000</v>
       </c>
       <c r="I35" s="3">
-        <v>7181600</v>
+        <v>8498100</v>
       </c>
       <c r="J35" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="K35" s="3">
         <v>6731300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5808400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6207300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4994100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4584200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6256400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>258716000</v>
+        <v>261605000</v>
       </c>
       <c r="E41" s="3">
-        <v>245585000</v>
+        <v>259455000</v>
       </c>
       <c r="F41" s="3">
-        <v>180477000</v>
+        <v>246287000</v>
       </c>
       <c r="G41" s="3">
-        <v>129702000</v>
+        <v>180992000</v>
       </c>
       <c r="H41" s="3">
-        <v>140251000</v>
+        <v>130073000</v>
       </c>
       <c r="I41" s="3">
-        <v>148941000</v>
+        <v>140652000</v>
       </c>
       <c r="J41" s="3">
+        <v>149367000</v>
+      </c>
+      <c r="K41" s="3">
         <v>113303000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134322000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>143547000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>159238000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>189156000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>163058000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>234107000</v>
+        <v>309253000</v>
       </c>
       <c r="E42" s="3">
-        <v>158559000</v>
+        <v>234776000</v>
       </c>
       <c r="F42" s="3">
-        <v>160887000</v>
+        <v>159012000</v>
       </c>
       <c r="G42" s="3">
-        <v>171711000</v>
+        <v>161347000</v>
       </c>
       <c r="H42" s="3">
-        <v>176763000</v>
+        <v>172202000</v>
       </c>
       <c r="I42" s="3">
-        <v>151199000</v>
+        <v>177268000</v>
       </c>
       <c r="J42" s="3">
+        <v>151631000</v>
+      </c>
+      <c r="K42" s="3">
         <v>151565000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>116234000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>124218000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>114921000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>219900000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>223436000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8262300</v>
+        <v>8319600</v>
       </c>
       <c r="E47" s="3">
-        <v>8164600</v>
+        <v>8285900</v>
       </c>
       <c r="F47" s="3">
-        <v>8269900</v>
+        <v>8188000</v>
       </c>
       <c r="G47" s="3">
-        <v>9517600</v>
+        <v>8293500</v>
       </c>
       <c r="H47" s="3">
-        <v>8233000</v>
+        <v>9544800</v>
       </c>
       <c r="I47" s="3">
-        <v>6709600</v>
+        <v>8256500</v>
       </c>
       <c r="J47" s="3">
+        <v>6728800</v>
+      </c>
+      <c r="K47" s="3">
         <v>5247100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3318600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3546500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10661700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4890500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4877200</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>36969200</v>
+        <v>36867000</v>
       </c>
       <c r="E48" s="3">
-        <v>36153300</v>
+        <v>37074800</v>
       </c>
       <c r="F48" s="3">
-        <v>35517500</v>
+        <v>36256600</v>
       </c>
       <c r="G48" s="3">
-        <v>38230000</v>
+        <v>35619000</v>
       </c>
       <c r="H48" s="3">
-        <v>28380300</v>
+        <v>38339200</v>
       </c>
       <c r="I48" s="3">
-        <v>24926800</v>
+        <v>28461400</v>
       </c>
       <c r="J48" s="3">
+        <v>24998000</v>
+      </c>
+      <c r="K48" s="3">
         <v>25265300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25846700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27621800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38028400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>15218300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16252600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>20229800</v>
+        <v>21621600</v>
       </c>
       <c r="E49" s="3">
-        <v>17993600</v>
+        <v>20287600</v>
       </c>
       <c r="F49" s="3">
-        <v>17260200</v>
+        <v>18045100</v>
       </c>
       <c r="G49" s="3">
-        <v>30040400</v>
+        <v>17309500</v>
       </c>
       <c r="H49" s="3">
-        <v>30987600</v>
+        <v>30126200</v>
       </c>
       <c r="I49" s="3">
-        <v>31121100</v>
+        <v>31076100</v>
       </c>
       <c r="J49" s="3">
+        <v>31210000</v>
+      </c>
+      <c r="K49" s="3">
         <v>31921800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>30042100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>32105500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>60412900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>30812100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>32964100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27759700</v>
+        <v>26965300</v>
       </c>
       <c r="E52" s="3">
-        <v>27688100</v>
+        <v>27839000</v>
       </c>
       <c r="F52" s="3">
-        <v>26393700</v>
+        <v>27767200</v>
       </c>
       <c r="G52" s="3">
-        <v>30664300</v>
+        <v>26469100</v>
       </c>
       <c r="H52" s="3">
-        <v>32223400</v>
+        <v>30751900</v>
       </c>
       <c r="I52" s="3">
-        <v>42417000</v>
+        <v>32315500</v>
       </c>
       <c r="J52" s="3">
+        <v>42538200</v>
+      </c>
+      <c r="K52" s="3">
         <v>29899300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29070300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31066900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31381100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29252900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29758400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1882110000</v>
+        <v>1955380000</v>
       </c>
       <c r="E54" s="3">
-        <v>1731480000</v>
+        <v>1887480000</v>
       </c>
       <c r="F54" s="3">
-        <v>1636450000</v>
+        <v>1736430000</v>
       </c>
       <c r="G54" s="3">
-        <v>1652120000</v>
+        <v>1641130000</v>
       </c>
       <c r="H54" s="3">
-        <v>1583310000</v>
+        <v>1656840000</v>
       </c>
       <c r="I54" s="3">
-        <v>1567070000</v>
+        <v>1587830000</v>
       </c>
       <c r="J54" s="3">
+        <v>1571550000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1452950000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1368140000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1462100000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1334680000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1394020000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1468450000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,8 +2654,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2566,9 +2696,12 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2608,51 +2741,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3298400</v>
+        <v>4184800</v>
       </c>
       <c r="E59" s="3">
-        <v>2372900</v>
+        <v>3307800</v>
       </c>
       <c r="F59" s="3">
-        <v>2548700</v>
+        <v>2379700</v>
       </c>
       <c r="G59" s="3">
-        <v>3038000</v>
+        <v>2555900</v>
       </c>
       <c r="H59" s="3">
-        <v>2785200</v>
+        <v>3046700</v>
       </c>
       <c r="I59" s="3">
-        <v>2989200</v>
+        <v>2793200</v>
       </c>
       <c r="J59" s="3">
+        <v>2997700</v>
+      </c>
+      <c r="K59" s="3">
         <v>2906700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2204900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2356400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5088600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5667900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5987600</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>304168000</v>
+        <v>335765000</v>
       </c>
       <c r="E61" s="3">
-        <v>267087000</v>
+        <v>305037000</v>
       </c>
       <c r="F61" s="3">
-        <v>255267000</v>
+        <v>267850000</v>
       </c>
       <c r="G61" s="3">
-        <v>284245000</v>
+        <v>255996000</v>
       </c>
       <c r="H61" s="3">
-        <v>267582000</v>
+        <v>285057000</v>
       </c>
       <c r="I61" s="3">
-        <v>236493000</v>
+        <v>268346000</v>
       </c>
       <c r="J61" s="3">
+        <v>237169000</v>
+      </c>
+      <c r="K61" s="3">
         <v>248323000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>230887000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>246744000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>229210000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>246179000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>258666000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15816000</v>
+        <v>15806800</v>
       </c>
       <c r="E62" s="3">
-        <v>17408800</v>
+        <v>15861200</v>
       </c>
       <c r="F62" s="3">
-        <v>18211700</v>
+        <v>17458600</v>
       </c>
       <c r="G62" s="3">
-        <v>22252300</v>
+        <v>18263800</v>
       </c>
       <c r="H62" s="3">
-        <v>20390400</v>
+        <v>22315800</v>
       </c>
       <c r="I62" s="3">
-        <v>20968700</v>
+        <v>20448700</v>
       </c>
       <c r="J62" s="3">
+        <v>21028600</v>
+      </c>
+      <c r="K62" s="3">
         <v>21866000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20476200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21882600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36961400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20588600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>23680400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1785430000</v>
+        <v>1851550000</v>
       </c>
       <c r="E66" s="3">
-        <v>1637160000</v>
+        <v>1790530000</v>
       </c>
       <c r="F66" s="3">
-        <v>1548050000</v>
+        <v>1641840000</v>
       </c>
       <c r="G66" s="3">
-        <v>1543550000</v>
+        <v>1552470000</v>
       </c>
       <c r="H66" s="3">
-        <v>1478640000</v>
+        <v>1547960000</v>
       </c>
       <c r="I66" s="3">
-        <v>1464550000</v>
+        <v>1482860000</v>
       </c>
       <c r="J66" s="3">
+        <v>1468730000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1354280000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1278270000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1366060000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1250550000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1315120000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1381050000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>82793100</v>
+        <v>92695200</v>
       </c>
       <c r="E72" s="3">
-        <v>74210700</v>
+        <v>83029600</v>
       </c>
       <c r="F72" s="3">
-        <v>61641000</v>
+        <v>74422800</v>
       </c>
       <c r="G72" s="3">
-        <v>73284200</v>
+        <v>61817100</v>
       </c>
       <c r="H72" s="3">
-        <v>70054100</v>
+        <v>73493500</v>
       </c>
       <c r="I72" s="3">
-        <v>65160800</v>
+        <v>70254300</v>
       </c>
       <c r="J72" s="3">
+        <v>65346900</v>
+      </c>
+      <c r="K72" s="3">
         <v>60930300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52801900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>56428400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>140362000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42600200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43125800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>96677800</v>
+        <v>103830000</v>
       </c>
       <c r="E76" s="3">
-        <v>94319100</v>
+        <v>96954100</v>
       </c>
       <c r="F76" s="3">
-        <v>88401500</v>
+        <v>94588500</v>
       </c>
       <c r="G76" s="3">
-        <v>108577000</v>
+        <v>88654000</v>
       </c>
       <c r="H76" s="3">
-        <v>104672000</v>
+        <v>108887000</v>
       </c>
       <c r="I76" s="3">
-        <v>102521000</v>
+        <v>104971000</v>
       </c>
       <c r="J76" s="3">
+        <v>102814000</v>
+      </c>
+      <c r="K76" s="3">
         <v>98667700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89871200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>96043700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>84126400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>78902300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>87401900</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>10421400</v>
+        <v>12051800</v>
       </c>
       <c r="E81" s="3">
-        <v>8814500</v>
+        <v>10451200</v>
       </c>
       <c r="F81" s="3">
-        <v>-9516500</v>
+        <v>8839700</v>
       </c>
       <c r="G81" s="3">
-        <v>7068800</v>
+        <v>-9543700</v>
       </c>
       <c r="H81" s="3">
-        <v>8473900</v>
+        <v>7089000</v>
       </c>
       <c r="I81" s="3">
-        <v>7181600</v>
+        <v>8498100</v>
       </c>
       <c r="J81" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="K81" s="3">
         <v>6731300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5808400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6207300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4994100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4584200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6256400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3238700</v>
+        <v>3464500</v>
       </c>
       <c r="E83" s="3">
-        <v>2990300</v>
+        <v>3248000</v>
       </c>
       <c r="F83" s="3">
-        <v>3048900</v>
+        <v>2998800</v>
       </c>
       <c r="G83" s="3">
-        <v>3256100</v>
+        <v>3057600</v>
       </c>
       <c r="H83" s="3">
-        <v>2631100</v>
+        <v>3265400</v>
       </c>
       <c r="I83" s="3">
-        <v>2813400</v>
+        <v>2638600</v>
       </c>
       <c r="J83" s="3">
+        <v>2821400</v>
+      </c>
+      <c r="K83" s="3">
         <v>2564900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2468300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>2860100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>2462700</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>30061000</v>
+        <v>5456800</v>
       </c>
       <c r="E89" s="3">
-        <v>61509700</v>
+        <v>30146900</v>
       </c>
       <c r="F89" s="3">
-        <v>71776000</v>
+        <v>61685500</v>
       </c>
       <c r="G89" s="3">
-        <v>3677100</v>
+        <v>71981100</v>
       </c>
       <c r="H89" s="3">
-        <v>3706400</v>
+        <v>3687600</v>
       </c>
       <c r="I89" s="3">
-        <v>43604000</v>
+        <v>3716900</v>
       </c>
       <c r="J89" s="3">
+        <v>43728600</v>
+      </c>
+      <c r="K89" s="3">
         <v>23678000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5796100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4297100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-41690000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26498000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>42143300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-9836600</v>
+        <v>-12454400</v>
       </c>
       <c r="E91" s="3">
-        <v>-10866300</v>
+        <v>-9864700</v>
       </c>
       <c r="F91" s="3">
-        <v>-8013800</v>
+        <v>-10897300</v>
       </c>
       <c r="G91" s="3">
-        <v>-13851100</v>
+        <v>-8036700</v>
       </c>
       <c r="H91" s="3">
-        <v>-11637700</v>
+        <v>-13890700</v>
       </c>
       <c r="I91" s="3">
-        <v>-8083300</v>
+        <v>-11671000</v>
       </c>
       <c r="J91" s="3">
+        <v>-8106300</v>
+      </c>
+      <c r="K91" s="3">
         <v>-7130600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7823400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7303600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2245300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2372800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3988600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4229300</v>
+        <v>-5838700</v>
       </c>
       <c r="E94" s="3">
-        <v>-4030800</v>
+        <v>-4241400</v>
       </c>
       <c r="F94" s="3">
-        <v>-7833700</v>
+        <v>-4042300</v>
       </c>
       <c r="G94" s="3">
-        <v>-7843500</v>
+        <v>-7856100</v>
       </c>
       <c r="H94" s="3">
-        <v>3415600</v>
+        <v>-7865900</v>
       </c>
       <c r="I94" s="3">
-        <v>-4348700</v>
+        <v>3425300</v>
       </c>
       <c r="J94" s="3">
+        <v>-4361100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14933900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6347300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>809800</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-8226100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2005100</v>
+        <v>-2460200</v>
       </c>
       <c r="E96" s="3">
-        <v>-1424600</v>
+        <v>-2010800</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-1428700</v>
       </c>
       <c r="G96" s="3">
-        <v>-4093700</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-3383000</v>
+        <v>-4105400</v>
       </c>
       <c r="I96" s="3">
-        <v>-2891500</v>
+        <v>-3392700</v>
       </c>
       <c r="J96" s="3">
+        <v>-2899800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-2505300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1529200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-991600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-978500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1413100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-4095400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-10810900</v>
+        <v>-2562500</v>
       </c>
       <c r="E100" s="3">
-        <v>-1434400</v>
+        <v>-10841800</v>
       </c>
       <c r="F100" s="3">
-        <v>-2071300</v>
+        <v>-1438500</v>
       </c>
       <c r="G100" s="3">
-        <v>-10982400</v>
+        <v>-2077200</v>
       </c>
       <c r="H100" s="3">
-        <v>-3581600</v>
+        <v>-11013700</v>
       </c>
       <c r="I100" s="3">
-        <v>4563500</v>
+        <v>-3591800</v>
       </c>
       <c r="J100" s="3">
+        <v>4576500</v>
+      </c>
+      <c r="K100" s="3">
         <v>-6233300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9146400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-2004800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-9520800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1584100</v>
+        <v>-350400</v>
       </c>
       <c r="E101" s="3">
-        <v>5637700</v>
+        <v>-1588600</v>
       </c>
       <c r="F101" s="3">
-        <v>-4613400</v>
+        <v>5653800</v>
       </c>
       <c r="G101" s="3">
-        <v>1482100</v>
+        <v>-4626600</v>
       </c>
       <c r="H101" s="3">
-        <v>-645600</v>
+        <v>1486300</v>
       </c>
       <c r="I101" s="3">
-        <v>-6341800</v>
+        <v>-647400</v>
       </c>
       <c r="J101" s="3">
+        <v>-6359900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-3917900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-532900</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>-6619800</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-2401600</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>13436600</v>
+        <v>-2971600</v>
       </c>
       <c r="E102" s="3">
-        <v>61682300</v>
+        <v>13475000</v>
       </c>
       <c r="F102" s="3">
-        <v>57257600</v>
+        <v>61858500</v>
       </c>
       <c r="G102" s="3">
-        <v>-13666700</v>
+        <v>57421200</v>
       </c>
       <c r="H102" s="3">
-        <v>2894800</v>
+        <v>-13705700</v>
       </c>
       <c r="I102" s="3">
-        <v>37477000</v>
+        <v>2903100</v>
       </c>
       <c r="J102" s="3">
+        <v>37584100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1407200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8062300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8372700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-49504700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24116500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>21994900</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>114524700</v>
+        <v>113745800</v>
       </c>
       <c r="E8" s="3">
-        <v>77723000</v>
+        <v>77194400</v>
       </c>
       <c r="F8" s="3">
-        <v>50556400</v>
+        <v>50212600</v>
       </c>
       <c r="G8" s="3">
-        <v>49770800</v>
+        <v>49432300</v>
       </c>
       <c r="H8" s="3">
-        <v>61787800</v>
+        <v>61367500</v>
       </c>
       <c r="I8" s="3">
-        <v>59111000</v>
+        <v>58709000</v>
       </c>
       <c r="J8" s="3">
-        <v>60978200</v>
+        <v>60563500</v>
       </c>
       <c r="K8" s="3">
         <v>59844300</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-3464500</v>
+        <v>-3440900</v>
       </c>
       <c r="E15" s="3">
-        <v>-3248000</v>
+        <v>-3225900</v>
       </c>
       <c r="F15" s="3">
-        <v>-2998800</v>
+        <v>-2978400</v>
       </c>
       <c r="G15" s="3">
-        <v>-3057600</v>
+        <v>-3036800</v>
       </c>
       <c r="H15" s="3">
-        <v>-3265400</v>
+        <v>-3243200</v>
       </c>
       <c r="I15" s="3">
-        <v>-2638600</v>
+        <v>-2620700</v>
       </c>
       <c r="J15" s="3">
-        <v>-2821400</v>
+        <v>-2802300</v>
       </c>
       <c r="K15" s="3">
         <v>-2564900</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>81502000</v>
+        <v>80947700</v>
       </c>
       <c r="E17" s="3">
-        <v>47514100</v>
+        <v>47190900</v>
       </c>
       <c r="F17" s="3">
-        <v>22285400</v>
+        <v>22133800</v>
       </c>
       <c r="G17" s="3">
-        <v>28410300</v>
+        <v>28217100</v>
       </c>
       <c r="H17" s="3">
-        <v>33559200</v>
+        <v>33330900</v>
       </c>
       <c r="I17" s="3">
-        <v>31521200</v>
+        <v>31306800</v>
       </c>
       <c r="J17" s="3">
-        <v>33715900</v>
+        <v>33486600</v>
       </c>
       <c r="K17" s="3">
         <v>36482000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33022700</v>
+        <v>32798200</v>
       </c>
       <c r="E18" s="3">
-        <v>30208900</v>
+        <v>30003500</v>
       </c>
       <c r="F18" s="3">
-        <v>28271000</v>
+        <v>28078700</v>
       </c>
       <c r="G18" s="3">
-        <v>21360500</v>
+        <v>21215200</v>
       </c>
       <c r="H18" s="3">
-        <v>28228600</v>
+        <v>28036600</v>
       </c>
       <c r="I18" s="3">
-        <v>27589900</v>
+        <v>27402200</v>
       </c>
       <c r="J18" s="3">
-        <v>27262300</v>
+        <v>27076900</v>
       </c>
       <c r="K18" s="3">
         <v>23362200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15113700</v>
+        <v>-15010900</v>
       </c>
       <c r="E20" s="3">
-        <v>-13615400</v>
+        <v>-13522800</v>
       </c>
       <c r="F20" s="3">
-        <v>-12442400</v>
+        <v>-12357800</v>
       </c>
       <c r="G20" s="3">
-        <v>-23619400</v>
+        <v>-23458800</v>
       </c>
       <c r="H20" s="3">
-        <v>-14580500</v>
+        <v>-14481400</v>
       </c>
       <c r="I20" s="3">
-        <v>-12137800</v>
+        <v>-12055200</v>
       </c>
       <c r="J20" s="3">
-        <v>-14106100</v>
+        <v>-14010200</v>
       </c>
       <c r="K20" s="3">
         <v>-11678900</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21394200</v>
+        <v>21206500</v>
       </c>
       <c r="E21" s="3">
-        <v>19860900</v>
+        <v>19686200</v>
       </c>
       <c r="F21" s="3">
-        <v>18845300</v>
+        <v>18680600</v>
       </c>
       <c r="G21" s="3">
-        <v>816900</v>
+        <v>774100</v>
       </c>
       <c r="H21" s="3">
-        <v>16932900</v>
+        <v>16778000</v>
       </c>
       <c r="I21" s="3">
-        <v>18106500</v>
+        <v>17951200</v>
       </c>
       <c r="J21" s="3">
-        <v>15994500</v>
+        <v>15851300</v>
       </c>
       <c r="K21" s="3">
         <v>14247300</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>17909000</v>
+        <v>17787200</v>
       </c>
       <c r="E23" s="3">
-        <v>16593500</v>
+        <v>16480700</v>
       </c>
       <c r="F23" s="3">
-        <v>15828600</v>
+        <v>15720900</v>
       </c>
       <c r="G23" s="3">
-        <v>-2258900</v>
+        <v>-2243500</v>
       </c>
       <c r="H23" s="3">
-        <v>13648000</v>
+        <v>13555200</v>
       </c>
       <c r="I23" s="3">
-        <v>15452100</v>
+        <v>15347000</v>
       </c>
       <c r="J23" s="3">
-        <v>13156200</v>
+        <v>13066700</v>
       </c>
       <c r="K23" s="3">
         <v>11683300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4652700</v>
+        <v>4621100</v>
       </c>
       <c r="E24" s="3">
-        <v>4881200</v>
+        <v>4848000</v>
       </c>
       <c r="F24" s="3">
-        <v>5325200</v>
+        <v>5288900</v>
       </c>
       <c r="G24" s="3">
-        <v>6128200</v>
+        <v>6086500</v>
       </c>
       <c r="H24" s="3">
-        <v>4817000</v>
+        <v>4784300</v>
       </c>
       <c r="I24" s="3">
-        <v>5316500</v>
+        <v>5280300</v>
       </c>
       <c r="J24" s="3">
-        <v>4226200</v>
+        <v>4197400</v>
       </c>
       <c r="K24" s="3">
         <v>3561000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>13256300</v>
+        <v>13166200</v>
       </c>
       <c r="E26" s="3">
-        <v>11712300</v>
+        <v>11632700</v>
       </c>
       <c r="F26" s="3">
-        <v>10503400</v>
+        <v>10432000</v>
       </c>
       <c r="G26" s="3">
-        <v>-8387100</v>
+        <v>-8330000</v>
       </c>
       <c r="H26" s="3">
-        <v>8831000</v>
+        <v>8771000</v>
       </c>
       <c r="I26" s="3">
-        <v>10135700</v>
+        <v>10066700</v>
       </c>
       <c r="J26" s="3">
-        <v>8930000</v>
+        <v>8869300</v>
       </c>
       <c r="K26" s="3">
         <v>8122300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12051800</v>
+        <v>11969800</v>
       </c>
       <c r="E27" s="3">
-        <v>10451200</v>
+        <v>10380100</v>
       </c>
       <c r="F27" s="3">
-        <v>8839700</v>
+        <v>8779600</v>
       </c>
       <c r="G27" s="3">
-        <v>-9543700</v>
+        <v>-9478800</v>
       </c>
       <c r="H27" s="3">
-        <v>7089000</v>
+        <v>7040800</v>
       </c>
       <c r="I27" s="3">
-        <v>8498100</v>
+        <v>8440300</v>
       </c>
       <c r="J27" s="3">
-        <v>7202100</v>
+        <v>7153200</v>
       </c>
       <c r="K27" s="3">
         <v>6731300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15113700</v>
+        <v>15010900</v>
       </c>
       <c r="E32" s="3">
-        <v>13615400</v>
+        <v>13522800</v>
       </c>
       <c r="F32" s="3">
-        <v>12442400</v>
+        <v>12357800</v>
       </c>
       <c r="G32" s="3">
-        <v>23619400</v>
+        <v>23458800</v>
       </c>
       <c r="H32" s="3">
-        <v>14580500</v>
+        <v>14481400</v>
       </c>
       <c r="I32" s="3">
-        <v>12137800</v>
+        <v>12055200</v>
       </c>
       <c r="J32" s="3">
-        <v>14106100</v>
+        <v>14010200</v>
       </c>
       <c r="K32" s="3">
         <v>11678900</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12051800</v>
+        <v>11969800</v>
       </c>
       <c r="E33" s="3">
-        <v>10451200</v>
+        <v>10380100</v>
       </c>
       <c r="F33" s="3">
-        <v>8839700</v>
+        <v>8779600</v>
       </c>
       <c r="G33" s="3">
-        <v>-9543700</v>
+        <v>-9478800</v>
       </c>
       <c r="H33" s="3">
-        <v>7089000</v>
+        <v>7040800</v>
       </c>
       <c r="I33" s="3">
-        <v>8498100</v>
+        <v>8440300</v>
       </c>
       <c r="J33" s="3">
-        <v>7202100</v>
+        <v>7153200</v>
       </c>
       <c r="K33" s="3">
         <v>6731300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12051800</v>
+        <v>11969800</v>
       </c>
       <c r="E35" s="3">
-        <v>10451200</v>
+        <v>10380100</v>
       </c>
       <c r="F35" s="3">
-        <v>8839700</v>
+        <v>8779600</v>
       </c>
       <c r="G35" s="3">
-        <v>-9543700</v>
+        <v>-9478800</v>
       </c>
       <c r="H35" s="3">
-        <v>7089000</v>
+        <v>7040800</v>
       </c>
       <c r="I35" s="3">
-        <v>8498100</v>
+        <v>8440300</v>
       </c>
       <c r="J35" s="3">
-        <v>7202100</v>
+        <v>7153200</v>
       </c>
       <c r="K35" s="3">
         <v>6731300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>261605000</v>
+        <v>259826000</v>
       </c>
       <c r="E41" s="3">
-        <v>259455000</v>
+        <v>257691000</v>
       </c>
       <c r="F41" s="3">
-        <v>246287000</v>
+        <v>244612000</v>
       </c>
       <c r="G41" s="3">
-        <v>180992000</v>
+        <v>179762000</v>
       </c>
       <c r="H41" s="3">
-        <v>130073000</v>
+        <v>129188000</v>
       </c>
       <c r="I41" s="3">
-        <v>140652000</v>
+        <v>139696000</v>
       </c>
       <c r="J41" s="3">
-        <v>149367000</v>
+        <v>148351000</v>
       </c>
       <c r="K41" s="3">
         <v>113303000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>309253000</v>
+        <v>307150000</v>
       </c>
       <c r="E42" s="3">
-        <v>234776000</v>
+        <v>233179000</v>
       </c>
       <c r="F42" s="3">
-        <v>159012000</v>
+        <v>157930000</v>
       </c>
       <c r="G42" s="3">
-        <v>161347000</v>
+        <v>160249000</v>
       </c>
       <c r="H42" s="3">
-        <v>172202000</v>
+        <v>171031000</v>
       </c>
       <c r="I42" s="3">
-        <v>177268000</v>
+        <v>176062000</v>
       </c>
       <c r="J42" s="3">
-        <v>151631000</v>
+        <v>150600000</v>
       </c>
       <c r="K42" s="3">
         <v>151565000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8319600</v>
+        <v>8263000</v>
       </c>
       <c r="E47" s="3">
-        <v>8285900</v>
+        <v>8229500</v>
       </c>
       <c r="F47" s="3">
-        <v>8188000</v>
+        <v>8132300</v>
       </c>
       <c r="G47" s="3">
-        <v>8293500</v>
+        <v>8237100</v>
       </c>
       <c r="H47" s="3">
-        <v>9544800</v>
+        <v>9479900</v>
       </c>
       <c r="I47" s="3">
-        <v>8256500</v>
+        <v>8200400</v>
       </c>
       <c r="J47" s="3">
-        <v>6728800</v>
+        <v>6683000</v>
       </c>
       <c r="K47" s="3">
         <v>5247100</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>36867000</v>
+        <v>36616300</v>
       </c>
       <c r="E48" s="3">
-        <v>37074800</v>
+        <v>36822700</v>
       </c>
       <c r="F48" s="3">
-        <v>36256600</v>
+        <v>36010000</v>
       </c>
       <c r="G48" s="3">
-        <v>35619000</v>
+        <v>35376700</v>
       </c>
       <c r="H48" s="3">
-        <v>38339200</v>
+        <v>38078500</v>
       </c>
       <c r="I48" s="3">
-        <v>28461400</v>
+        <v>28267900</v>
       </c>
       <c r="J48" s="3">
-        <v>24998000</v>
+        <v>24828000</v>
       </c>
       <c r="K48" s="3">
         <v>25265300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21621600</v>
+        <v>21474600</v>
       </c>
       <c r="E49" s="3">
-        <v>20287600</v>
+        <v>20149700</v>
       </c>
       <c r="F49" s="3">
-        <v>18045100</v>
+        <v>17922300</v>
       </c>
       <c r="G49" s="3">
-        <v>17309500</v>
+        <v>17191800</v>
       </c>
       <c r="H49" s="3">
-        <v>30126200</v>
+        <v>29921300</v>
       </c>
       <c r="I49" s="3">
-        <v>31076100</v>
+        <v>30864800</v>
       </c>
       <c r="J49" s="3">
-        <v>31210000</v>
+        <v>30997700</v>
       </c>
       <c r="K49" s="3">
         <v>31921800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26965300</v>
+        <v>26781900</v>
       </c>
       <c r="E52" s="3">
-        <v>27839000</v>
+        <v>27649700</v>
       </c>
       <c r="F52" s="3">
-        <v>27767200</v>
+        <v>27578400</v>
       </c>
       <c r="G52" s="3">
-        <v>26469100</v>
+        <v>26289100</v>
       </c>
       <c r="H52" s="3">
-        <v>30751900</v>
+        <v>30542700</v>
       </c>
       <c r="I52" s="3">
-        <v>32315500</v>
+        <v>32095700</v>
       </c>
       <c r="J52" s="3">
-        <v>42538200</v>
+        <v>42248900</v>
       </c>
       <c r="K52" s="3">
         <v>29899300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1955380000</v>
+        <v>1942080000</v>
       </c>
       <c r="E54" s="3">
-        <v>1887480000</v>
+        <v>1874650000</v>
       </c>
       <c r="F54" s="3">
-        <v>1736430000</v>
+        <v>1724620000</v>
       </c>
       <c r="G54" s="3">
-        <v>1641130000</v>
+        <v>1629970000</v>
       </c>
       <c r="H54" s="3">
-        <v>1656840000</v>
+        <v>1645580000</v>
       </c>
       <c r="I54" s="3">
-        <v>1587830000</v>
+        <v>1577030000</v>
       </c>
       <c r="J54" s="3">
-        <v>1571550000</v>
+        <v>1560860000</v>
       </c>
       <c r="K54" s="3">
         <v>1452950000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4184800</v>
+        <v>4156400</v>
       </c>
       <c r="E59" s="3">
-        <v>3307800</v>
+        <v>3285300</v>
       </c>
       <c r="F59" s="3">
-        <v>2379700</v>
+        <v>2363500</v>
       </c>
       <c r="G59" s="3">
-        <v>2555900</v>
+        <v>2538600</v>
       </c>
       <c r="H59" s="3">
-        <v>3046700</v>
+        <v>3026000</v>
       </c>
       <c r="I59" s="3">
-        <v>2793200</v>
+        <v>2774200</v>
       </c>
       <c r="J59" s="3">
-        <v>2997700</v>
+        <v>2977300</v>
       </c>
       <c r="K59" s="3">
         <v>2906700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>335765000</v>
+        <v>333481000</v>
       </c>
       <c r="E61" s="3">
-        <v>305037000</v>
+        <v>302962000</v>
       </c>
       <c r="F61" s="3">
-        <v>267850000</v>
+        <v>266028000</v>
       </c>
       <c r="G61" s="3">
-        <v>255996000</v>
+        <v>254255000</v>
       </c>
       <c r="H61" s="3">
-        <v>285057000</v>
+        <v>283119000</v>
       </c>
       <c r="I61" s="3">
-        <v>268346000</v>
+        <v>266521000</v>
       </c>
       <c r="J61" s="3">
-        <v>237169000</v>
+        <v>235556000</v>
       </c>
       <c r="K61" s="3">
         <v>248323000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15806800</v>
+        <v>15699300</v>
       </c>
       <c r="E62" s="3">
-        <v>15861200</v>
+        <v>15753400</v>
       </c>
       <c r="F62" s="3">
-        <v>17458600</v>
+        <v>17339800</v>
       </c>
       <c r="G62" s="3">
-        <v>18263800</v>
+        <v>18139500</v>
       </c>
       <c r="H62" s="3">
-        <v>22315800</v>
+        <v>22164100</v>
       </c>
       <c r="I62" s="3">
-        <v>20448700</v>
+        <v>20309600</v>
       </c>
       <c r="J62" s="3">
-        <v>21028600</v>
+        <v>20885600</v>
       </c>
       <c r="K62" s="3">
         <v>21866000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1851550000</v>
+        <v>1838960000</v>
       </c>
       <c r="E66" s="3">
-        <v>1790530000</v>
+        <v>1778350000</v>
       </c>
       <c r="F66" s="3">
-        <v>1641840000</v>
+        <v>1630670000</v>
       </c>
       <c r="G66" s="3">
-        <v>1552470000</v>
+        <v>1541910000</v>
       </c>
       <c r="H66" s="3">
-        <v>1547960000</v>
+        <v>1537430000</v>
       </c>
       <c r="I66" s="3">
-        <v>1482860000</v>
+        <v>1472780000</v>
       </c>
       <c r="J66" s="3">
-        <v>1468730000</v>
+        <v>1458750000</v>
       </c>
       <c r="K66" s="3">
         <v>1354280000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>92695200</v>
+        <v>92064800</v>
       </c>
       <c r="E72" s="3">
-        <v>83029600</v>
+        <v>82465000</v>
       </c>
       <c r="F72" s="3">
-        <v>74422800</v>
+        <v>73916600</v>
       </c>
       <c r="G72" s="3">
-        <v>61817100</v>
+        <v>61396700</v>
       </c>
       <c r="H72" s="3">
-        <v>73493500</v>
+        <v>72993700</v>
       </c>
       <c r="I72" s="3">
-        <v>70254300</v>
+        <v>69776500</v>
       </c>
       <c r="J72" s="3">
-        <v>65346900</v>
+        <v>64902500</v>
       </c>
       <c r="K72" s="3">
         <v>60930300</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>103830000</v>
+        <v>103124000</v>
       </c>
       <c r="E76" s="3">
-        <v>96954100</v>
+        <v>96294700</v>
       </c>
       <c r="F76" s="3">
-        <v>94588500</v>
+        <v>93945300</v>
       </c>
       <c r="G76" s="3">
-        <v>88654000</v>
+        <v>88051100</v>
       </c>
       <c r="H76" s="3">
-        <v>108887000</v>
+        <v>108147000</v>
       </c>
       <c r="I76" s="3">
-        <v>104971000</v>
+        <v>104257000</v>
       </c>
       <c r="J76" s="3">
-        <v>102814000</v>
+        <v>102114000</v>
       </c>
       <c r="K76" s="3">
         <v>98667700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12051800</v>
+        <v>11969800</v>
       </c>
       <c r="E81" s="3">
-        <v>10451200</v>
+        <v>10380100</v>
       </c>
       <c r="F81" s="3">
-        <v>8839700</v>
+        <v>8779600</v>
       </c>
       <c r="G81" s="3">
-        <v>-9543700</v>
+        <v>-9478800</v>
       </c>
       <c r="H81" s="3">
-        <v>7089000</v>
+        <v>7040800</v>
       </c>
       <c r="I81" s="3">
-        <v>8498100</v>
+        <v>8440300</v>
       </c>
       <c r="J81" s="3">
-        <v>7202100</v>
+        <v>7153200</v>
       </c>
       <c r="K81" s="3">
         <v>6731300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3464500</v>
+        <v>3440900</v>
       </c>
       <c r="E83" s="3">
-        <v>3248000</v>
+        <v>3225900</v>
       </c>
       <c r="F83" s="3">
-        <v>2998800</v>
+        <v>2978400</v>
       </c>
       <c r="G83" s="3">
-        <v>3057600</v>
+        <v>3036800</v>
       </c>
       <c r="H83" s="3">
-        <v>3265400</v>
+        <v>3243200</v>
       </c>
       <c r="I83" s="3">
-        <v>2638600</v>
+        <v>2620700</v>
       </c>
       <c r="J83" s="3">
-        <v>2821400</v>
+        <v>2802300</v>
       </c>
       <c r="K83" s="3">
         <v>2564900</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5456800</v>
+        <v>5419700</v>
       </c>
       <c r="E89" s="3">
-        <v>30146900</v>
+        <v>29941900</v>
       </c>
       <c r="F89" s="3">
-        <v>61685500</v>
+        <v>61266000</v>
       </c>
       <c r="G89" s="3">
-        <v>71981100</v>
+        <v>71491500</v>
       </c>
       <c r="H89" s="3">
-        <v>3687600</v>
+        <v>3662500</v>
       </c>
       <c r="I89" s="3">
-        <v>3716900</v>
+        <v>3691700</v>
       </c>
       <c r="J89" s="3">
-        <v>43728600</v>
+        <v>43431200</v>
       </c>
       <c r="K89" s="3">
         <v>23678000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12454400</v>
+        <v>-12369700</v>
       </c>
       <c r="E91" s="3">
-        <v>-9864700</v>
+        <v>-9797600</v>
       </c>
       <c r="F91" s="3">
-        <v>-10897300</v>
+        <v>-10823200</v>
       </c>
       <c r="G91" s="3">
-        <v>-8036700</v>
+        <v>-7982100</v>
       </c>
       <c r="H91" s="3">
-        <v>-13890700</v>
+        <v>-13796200</v>
       </c>
       <c r="I91" s="3">
-        <v>-11671000</v>
+        <v>-11591600</v>
       </c>
       <c r="J91" s="3">
-        <v>-8106300</v>
+        <v>-8051200</v>
       </c>
       <c r="K91" s="3">
         <v>-7130600</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5838700</v>
+        <v>-5799000</v>
       </c>
       <c r="E94" s="3">
-        <v>-4241400</v>
+        <v>-4212600</v>
       </c>
       <c r="F94" s="3">
-        <v>-4042300</v>
+        <v>-4014800</v>
       </c>
       <c r="G94" s="3">
-        <v>-7856100</v>
+        <v>-7802700</v>
       </c>
       <c r="H94" s="3">
-        <v>-7865900</v>
+        <v>-7812400</v>
       </c>
       <c r="I94" s="3">
-        <v>3425300</v>
+        <v>3402000</v>
       </c>
       <c r="J94" s="3">
-        <v>-4361100</v>
+        <v>-4331400</v>
       </c>
       <c r="K94" s="3">
         <v>-14933900</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2460200</v>
+        <v>-2443500</v>
       </c>
       <c r="E96" s="3">
-        <v>-2010800</v>
+        <v>-1997100</v>
       </c>
       <c r="F96" s="3">
-        <v>-1428700</v>
+        <v>-1419000</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-4105400</v>
+        <v>-4077500</v>
       </c>
       <c r="I96" s="3">
-        <v>-3392700</v>
+        <v>-3369600</v>
       </c>
       <c r="J96" s="3">
-        <v>-2899800</v>
+        <v>-2880100</v>
       </c>
       <c r="K96" s="3">
         <v>-2505300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2562500</v>
+        <v>-2545000</v>
       </c>
       <c r="E100" s="3">
-        <v>-10841800</v>
+        <v>-10768100</v>
       </c>
       <c r="F100" s="3">
-        <v>-1438500</v>
+        <v>-1428700</v>
       </c>
       <c r="G100" s="3">
-        <v>-2077200</v>
+        <v>-2063100</v>
       </c>
       <c r="H100" s="3">
-        <v>-11013700</v>
+        <v>-10938800</v>
       </c>
       <c r="I100" s="3">
-        <v>-3591800</v>
+        <v>-3567400</v>
       </c>
       <c r="J100" s="3">
-        <v>4576500</v>
+        <v>4545400</v>
       </c>
       <c r="K100" s="3">
         <v>-6233300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-350400</v>
+        <v>-348000</v>
       </c>
       <c r="E101" s="3">
-        <v>-1588600</v>
+        <v>-1577800</v>
       </c>
       <c r="F101" s="3">
-        <v>5653800</v>
+        <v>5615300</v>
       </c>
       <c r="G101" s="3">
-        <v>-4626600</v>
+        <v>-4595100</v>
       </c>
       <c r="H101" s="3">
-        <v>1486300</v>
+        <v>1476200</v>
       </c>
       <c r="I101" s="3">
-        <v>-647400</v>
+        <v>-643000</v>
       </c>
       <c r="J101" s="3">
-        <v>-6359900</v>
+        <v>-6316700</v>
       </c>
       <c r="K101" s="3">
         <v>-3917900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2971600</v>
+        <v>-2951400</v>
       </c>
       <c r="E102" s="3">
-        <v>13475000</v>
+        <v>13383400</v>
       </c>
       <c r="F102" s="3">
-        <v>61858500</v>
+        <v>61437800</v>
       </c>
       <c r="G102" s="3">
-        <v>57421200</v>
+        <v>57030700</v>
       </c>
       <c r="H102" s="3">
-        <v>-13705700</v>
+        <v>-13612500</v>
       </c>
       <c r="I102" s="3">
-        <v>2903100</v>
+        <v>2883300</v>
       </c>
       <c r="J102" s="3">
-        <v>37584100</v>
+        <v>37328500</v>
       </c>
       <c r="K102" s="3">
         <v>-1407200</v>

--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>113745800</v>
+        <v>116577100</v>
       </c>
       <c r="E8" s="3">
-        <v>77194400</v>
+        <v>79115900</v>
       </c>
       <c r="F8" s="3">
-        <v>50212600</v>
+        <v>51462400</v>
       </c>
       <c r="G8" s="3">
-        <v>49432300</v>
+        <v>50662700</v>
       </c>
       <c r="H8" s="3">
-        <v>61367500</v>
+        <v>62895100</v>
       </c>
       <c r="I8" s="3">
-        <v>58709000</v>
+        <v>60170400</v>
       </c>
       <c r="J8" s="3">
-        <v>60563500</v>
+        <v>62071000</v>
       </c>
       <c r="K8" s="3">
         <v>59844300</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-3440900</v>
+        <v>-3526600</v>
       </c>
       <c r="E15" s="3">
-        <v>-3225900</v>
+        <v>-3306200</v>
       </c>
       <c r="F15" s="3">
-        <v>-2978400</v>
+        <v>-3052500</v>
       </c>
       <c r="G15" s="3">
-        <v>-3036800</v>
+        <v>-3112400</v>
       </c>
       <c r="H15" s="3">
-        <v>-3243200</v>
+        <v>-3323900</v>
       </c>
       <c r="I15" s="3">
-        <v>-2620700</v>
+        <v>-2685900</v>
       </c>
       <c r="J15" s="3">
-        <v>-2802300</v>
+        <v>-2872000</v>
       </c>
       <c r="K15" s="3">
         <v>-2564900</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>80947700</v>
+        <v>82962600</v>
       </c>
       <c r="E17" s="3">
-        <v>47190900</v>
+        <v>48365600</v>
       </c>
       <c r="F17" s="3">
-        <v>22133800</v>
+        <v>22684800</v>
       </c>
       <c r="G17" s="3">
-        <v>28217100</v>
+        <v>28919400</v>
       </c>
       <c r="H17" s="3">
-        <v>33330900</v>
+        <v>34160600</v>
       </c>
       <c r="I17" s="3">
-        <v>31306800</v>
+        <v>32086100</v>
       </c>
       <c r="J17" s="3">
-        <v>33486600</v>
+        <v>34320100</v>
       </c>
       <c r="K17" s="3">
         <v>36482000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>32798200</v>
+        <v>33614600</v>
       </c>
       <c r="E18" s="3">
-        <v>30003500</v>
+        <v>30750300</v>
       </c>
       <c r="F18" s="3">
-        <v>28078700</v>
+        <v>28777700</v>
       </c>
       <c r="G18" s="3">
-        <v>21215200</v>
+        <v>21743300</v>
       </c>
       <c r="H18" s="3">
-        <v>28036600</v>
+        <v>28734500</v>
       </c>
       <c r="I18" s="3">
-        <v>27402200</v>
+        <v>28084300</v>
       </c>
       <c r="J18" s="3">
-        <v>27076900</v>
+        <v>27750900</v>
       </c>
       <c r="K18" s="3">
         <v>23362200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-15010900</v>
+        <v>-15384600</v>
       </c>
       <c r="E20" s="3">
-        <v>-13522800</v>
+        <v>-13859400</v>
       </c>
       <c r="F20" s="3">
-        <v>-12357800</v>
+        <v>-12665400</v>
       </c>
       <c r="G20" s="3">
-        <v>-23458800</v>
+        <v>-24042700</v>
       </c>
       <c r="H20" s="3">
-        <v>-14481400</v>
+        <v>-14841800</v>
       </c>
       <c r="I20" s="3">
-        <v>-12055200</v>
+        <v>-12355300</v>
       </c>
       <c r="J20" s="3">
-        <v>-14010200</v>
+        <v>-14358900</v>
       </c>
       <c r="K20" s="3">
         <v>-11678900</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21206500</v>
+        <v>21756000</v>
       </c>
       <c r="E21" s="3">
-        <v>19686200</v>
+        <v>20196500</v>
       </c>
       <c r="F21" s="3">
-        <v>18680600</v>
+        <v>19164300</v>
       </c>
       <c r="G21" s="3">
-        <v>774100</v>
+        <v>812400</v>
       </c>
       <c r="H21" s="3">
-        <v>16778000</v>
+        <v>17215900</v>
       </c>
       <c r="I21" s="3">
-        <v>17951200</v>
+        <v>18414500</v>
       </c>
       <c r="J21" s="3">
-        <v>15851300</v>
+        <v>16263500</v>
       </c>
       <c r="K21" s="3">
         <v>14247300</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>17787200</v>
+        <v>18230000</v>
       </c>
       <c r="E23" s="3">
-        <v>16480700</v>
+        <v>16890900</v>
       </c>
       <c r="F23" s="3">
-        <v>15720900</v>
+        <v>16112300</v>
       </c>
       <c r="G23" s="3">
-        <v>-2243500</v>
+        <v>-2299400</v>
       </c>
       <c r="H23" s="3">
-        <v>13555200</v>
+        <v>13892600</v>
       </c>
       <c r="I23" s="3">
-        <v>15347000</v>
+        <v>15729000</v>
       </c>
       <c r="J23" s="3">
-        <v>13066700</v>
+        <v>13392000</v>
       </c>
       <c r="K23" s="3">
         <v>11683300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4621100</v>
+        <v>4736100</v>
       </c>
       <c r="E24" s="3">
-        <v>4848000</v>
+        <v>4968700</v>
       </c>
       <c r="F24" s="3">
-        <v>5288900</v>
+        <v>5420600</v>
       </c>
       <c r="G24" s="3">
-        <v>6086500</v>
+        <v>6238000</v>
       </c>
       <c r="H24" s="3">
-        <v>4784300</v>
+        <v>4903300</v>
       </c>
       <c r="I24" s="3">
-        <v>5280300</v>
+        <v>5411700</v>
       </c>
       <c r="J24" s="3">
-        <v>4197400</v>
+        <v>4301900</v>
       </c>
       <c r="K24" s="3">
         <v>3561000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>13166200</v>
+        <v>13493900</v>
       </c>
       <c r="E26" s="3">
-        <v>11632700</v>
+        <v>11922200</v>
       </c>
       <c r="F26" s="3">
-        <v>10432000</v>
+        <v>10691700</v>
       </c>
       <c r="G26" s="3">
-        <v>-8330000</v>
+        <v>-8537400</v>
       </c>
       <c r="H26" s="3">
-        <v>8771000</v>
+        <v>8989300</v>
       </c>
       <c r="I26" s="3">
-        <v>10066700</v>
+        <v>10317300</v>
       </c>
       <c r="J26" s="3">
-        <v>8869300</v>
+        <v>9090100</v>
       </c>
       <c r="K26" s="3">
         <v>8122300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>11969800</v>
+        <v>12267800</v>
       </c>
       <c r="E27" s="3">
-        <v>10380100</v>
+        <v>10638500</v>
       </c>
       <c r="F27" s="3">
-        <v>8779600</v>
+        <v>8998100</v>
       </c>
       <c r="G27" s="3">
-        <v>-9478800</v>
+        <v>-9714800</v>
       </c>
       <c r="H27" s="3">
-        <v>7040800</v>
+        <v>7216000</v>
       </c>
       <c r="I27" s="3">
-        <v>8440300</v>
+        <v>8650400</v>
       </c>
       <c r="J27" s="3">
-        <v>7153200</v>
+        <v>7331200</v>
       </c>
       <c r="K27" s="3">
         <v>6731300</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>15010900</v>
+        <v>15384600</v>
       </c>
       <c r="E32" s="3">
-        <v>13522800</v>
+        <v>13859400</v>
       </c>
       <c r="F32" s="3">
-        <v>12357800</v>
+        <v>12665400</v>
       </c>
       <c r="G32" s="3">
-        <v>23458800</v>
+        <v>24042700</v>
       </c>
       <c r="H32" s="3">
-        <v>14481400</v>
+        <v>14841800</v>
       </c>
       <c r="I32" s="3">
-        <v>12055200</v>
+        <v>12355300</v>
       </c>
       <c r="J32" s="3">
-        <v>14010200</v>
+        <v>14358900</v>
       </c>
       <c r="K32" s="3">
         <v>11678900</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>11969800</v>
+        <v>12267800</v>
       </c>
       <c r="E33" s="3">
-        <v>10380100</v>
+        <v>10638500</v>
       </c>
       <c r="F33" s="3">
-        <v>8779600</v>
+        <v>8998100</v>
       </c>
       <c r="G33" s="3">
-        <v>-9478800</v>
+        <v>-9714800</v>
       </c>
       <c r="H33" s="3">
-        <v>7040800</v>
+        <v>7216000</v>
       </c>
       <c r="I33" s="3">
-        <v>8440300</v>
+        <v>8650400</v>
       </c>
       <c r="J33" s="3">
-        <v>7153200</v>
+        <v>7331200</v>
       </c>
       <c r="K33" s="3">
         <v>6731300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>11969800</v>
+        <v>12267800</v>
       </c>
       <c r="E35" s="3">
-        <v>10380100</v>
+        <v>10638500</v>
       </c>
       <c r="F35" s="3">
-        <v>8779600</v>
+        <v>8998100</v>
       </c>
       <c r="G35" s="3">
-        <v>-9478800</v>
+        <v>-9714800</v>
       </c>
       <c r="H35" s="3">
-        <v>7040800</v>
+        <v>7216000</v>
       </c>
       <c r="I35" s="3">
-        <v>8440300</v>
+        <v>8650400</v>
       </c>
       <c r="J35" s="3">
-        <v>7153200</v>
+        <v>7331200</v>
       </c>
       <c r="K35" s="3">
         <v>6731300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>259826000</v>
+        <v>266294000</v>
       </c>
       <c r="E41" s="3">
-        <v>257691000</v>
+        <v>264105000</v>
       </c>
       <c r="F41" s="3">
-        <v>244612000</v>
+        <v>250701000</v>
       </c>
       <c r="G41" s="3">
-        <v>179762000</v>
+        <v>184236000</v>
       </c>
       <c r="H41" s="3">
-        <v>129188000</v>
+        <v>132404000</v>
       </c>
       <c r="I41" s="3">
-        <v>139696000</v>
+        <v>143173000</v>
       </c>
       <c r="J41" s="3">
-        <v>148351000</v>
+        <v>152044000</v>
       </c>
       <c r="K41" s="3">
         <v>113303000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>307150000</v>
+        <v>314795000</v>
       </c>
       <c r="E42" s="3">
-        <v>233179000</v>
+        <v>238984000</v>
       </c>
       <c r="F42" s="3">
-        <v>157930000</v>
+        <v>161861000</v>
       </c>
       <c r="G42" s="3">
-        <v>160249000</v>
+        <v>164238000</v>
       </c>
       <c r="H42" s="3">
-        <v>171031000</v>
+        <v>175288000</v>
       </c>
       <c r="I42" s="3">
-        <v>176062000</v>
+        <v>180445000</v>
       </c>
       <c r="J42" s="3">
-        <v>150600000</v>
+        <v>154349000</v>
       </c>
       <c r="K42" s="3">
         <v>151565000</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8263000</v>
+        <v>8468700</v>
       </c>
       <c r="E47" s="3">
-        <v>8229500</v>
+        <v>8434400</v>
       </c>
       <c r="F47" s="3">
-        <v>8132300</v>
+        <v>8334700</v>
       </c>
       <c r="G47" s="3">
-        <v>8237100</v>
+        <v>8442100</v>
       </c>
       <c r="H47" s="3">
-        <v>9479900</v>
+        <v>9715900</v>
       </c>
       <c r="I47" s="3">
-        <v>8200400</v>
+        <v>8404500</v>
       </c>
       <c r="J47" s="3">
-        <v>6683000</v>
+        <v>6849400</v>
       </c>
       <c r="K47" s="3">
         <v>5247100</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>36616300</v>
+        <v>37527700</v>
       </c>
       <c r="E48" s="3">
-        <v>36822700</v>
+        <v>37739300</v>
       </c>
       <c r="F48" s="3">
-        <v>36010000</v>
+        <v>36906300</v>
       </c>
       <c r="G48" s="3">
-        <v>35376700</v>
+        <v>36257300</v>
       </c>
       <c r="H48" s="3">
-        <v>38078500</v>
+        <v>39026300</v>
       </c>
       <c r="I48" s="3">
-        <v>28267900</v>
+        <v>28971500</v>
       </c>
       <c r="J48" s="3">
-        <v>24828000</v>
+        <v>25446000</v>
       </c>
       <c r="K48" s="3">
         <v>25265300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21474600</v>
+        <v>22009100</v>
       </c>
       <c r="E49" s="3">
-        <v>20149700</v>
+        <v>20651200</v>
       </c>
       <c r="F49" s="3">
-        <v>17922300</v>
+        <v>18368400</v>
       </c>
       <c r="G49" s="3">
-        <v>17191800</v>
+        <v>17619700</v>
       </c>
       <c r="H49" s="3">
-        <v>29921300</v>
+        <v>30666100</v>
       </c>
       <c r="I49" s="3">
-        <v>30864800</v>
+        <v>31633100</v>
       </c>
       <c r="J49" s="3">
-        <v>30997700</v>
+        <v>31769300</v>
       </c>
       <c r="K49" s="3">
         <v>31921800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>26781900</v>
+        <v>27448500</v>
       </c>
       <c r="E52" s="3">
-        <v>27649700</v>
+        <v>28337900</v>
       </c>
       <c r="F52" s="3">
-        <v>27578400</v>
+        <v>28264800</v>
       </c>
       <c r="G52" s="3">
-        <v>26289100</v>
+        <v>26943500</v>
       </c>
       <c r="H52" s="3">
-        <v>30542700</v>
+        <v>31303000</v>
       </c>
       <c r="I52" s="3">
-        <v>32095700</v>
+        <v>32894600</v>
       </c>
       <c r="J52" s="3">
-        <v>42248900</v>
+        <v>43300500</v>
       </c>
       <c r="K52" s="3">
         <v>29899300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1942080000</v>
+        <v>1990430000</v>
       </c>
       <c r="E54" s="3">
-        <v>1874650000</v>
+        <v>1921310000</v>
       </c>
       <c r="F54" s="3">
-        <v>1724620000</v>
+        <v>1767550000</v>
       </c>
       <c r="G54" s="3">
-        <v>1629970000</v>
+        <v>1670540000</v>
       </c>
       <c r="H54" s="3">
-        <v>1645580000</v>
+        <v>1686540000</v>
       </c>
       <c r="I54" s="3">
-        <v>1577030000</v>
+        <v>1616290000</v>
       </c>
       <c r="J54" s="3">
-        <v>1560860000</v>
+        <v>1599710000</v>
       </c>
       <c r="K54" s="3">
         <v>1452950000</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4156400</v>
+        <v>4259800</v>
       </c>
       <c r="E59" s="3">
-        <v>3285300</v>
+        <v>3367100</v>
       </c>
       <c r="F59" s="3">
-        <v>2363500</v>
+        <v>2422300</v>
       </c>
       <c r="G59" s="3">
-        <v>2538600</v>
+        <v>2601800</v>
       </c>
       <c r="H59" s="3">
-        <v>3026000</v>
+        <v>3101300</v>
       </c>
       <c r="I59" s="3">
-        <v>2774200</v>
+        <v>2843200</v>
       </c>
       <c r="J59" s="3">
-        <v>2977300</v>
+        <v>3051400</v>
       </c>
       <c r="K59" s="3">
         <v>2906700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>333481000</v>
+        <v>341782000</v>
       </c>
       <c r="E61" s="3">
-        <v>302962000</v>
+        <v>310504000</v>
       </c>
       <c r="F61" s="3">
-        <v>266028000</v>
+        <v>272650000</v>
       </c>
       <c r="G61" s="3">
-        <v>254255000</v>
+        <v>260584000</v>
       </c>
       <c r="H61" s="3">
-        <v>283119000</v>
+        <v>290166000</v>
       </c>
       <c r="I61" s="3">
-        <v>266521000</v>
+        <v>273155000</v>
       </c>
       <c r="J61" s="3">
-        <v>235556000</v>
+        <v>241419000</v>
       </c>
       <c r="K61" s="3">
         <v>248323000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>15699300</v>
+        <v>16090100</v>
       </c>
       <c r="E62" s="3">
-        <v>15753400</v>
+        <v>16145500</v>
       </c>
       <c r="F62" s="3">
-        <v>17339800</v>
+        <v>17771400</v>
       </c>
       <c r="G62" s="3">
-        <v>18139500</v>
+        <v>18591100</v>
       </c>
       <c r="H62" s="3">
-        <v>22164100</v>
+        <v>22715800</v>
       </c>
       <c r="I62" s="3">
-        <v>20309600</v>
+        <v>20815100</v>
       </c>
       <c r="J62" s="3">
-        <v>20885600</v>
+        <v>21405500</v>
       </c>
       <c r="K62" s="3">
         <v>21866000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1838960000</v>
+        <v>1884740000</v>
       </c>
       <c r="E66" s="3">
-        <v>1778350000</v>
+        <v>1822620000</v>
       </c>
       <c r="F66" s="3">
-        <v>1630670000</v>
+        <v>1671260000</v>
       </c>
       <c r="G66" s="3">
-        <v>1541910000</v>
+        <v>1580290000</v>
       </c>
       <c r="H66" s="3">
-        <v>1537430000</v>
+        <v>1575700000</v>
       </c>
       <c r="I66" s="3">
-        <v>1472780000</v>
+        <v>1509440000</v>
       </c>
       <c r="J66" s="3">
-        <v>1458750000</v>
+        <v>1495060000</v>
       </c>
       <c r="K66" s="3">
         <v>1354280000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>92064800</v>
+        <v>94356400</v>
       </c>
       <c r="E72" s="3">
-        <v>82465000</v>
+        <v>84517600</v>
       </c>
       <c r="F72" s="3">
-        <v>73916600</v>
+        <v>75756500</v>
       </c>
       <c r="G72" s="3">
-        <v>61396700</v>
+        <v>62925000</v>
       </c>
       <c r="H72" s="3">
-        <v>72993700</v>
+        <v>74810600</v>
       </c>
       <c r="I72" s="3">
-        <v>69776500</v>
+        <v>71513300</v>
       </c>
       <c r="J72" s="3">
-        <v>64902500</v>
+        <v>66518000</v>
       </c>
       <c r="K72" s="3">
         <v>60930300</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>103124000</v>
+        <v>105691000</v>
       </c>
       <c r="E76" s="3">
-        <v>96294700</v>
+        <v>98691600</v>
       </c>
       <c r="F76" s="3">
-        <v>93945300</v>
+        <v>96283700</v>
       </c>
       <c r="G76" s="3">
-        <v>88051100</v>
+        <v>90242800</v>
       </c>
       <c r="H76" s="3">
-        <v>108147000</v>
+        <v>110839000</v>
       </c>
       <c r="I76" s="3">
-        <v>104257000</v>
+        <v>106852000</v>
       </c>
       <c r="J76" s="3">
-        <v>102114000</v>
+        <v>104656000</v>
       </c>
       <c r="K76" s="3">
         <v>98667700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>11969800</v>
+        <v>12267800</v>
       </c>
       <c r="E81" s="3">
-        <v>10380100</v>
+        <v>10638500</v>
       </c>
       <c r="F81" s="3">
-        <v>8779600</v>
+        <v>8998100</v>
       </c>
       <c r="G81" s="3">
-        <v>-9478800</v>
+        <v>-9714800</v>
       </c>
       <c r="H81" s="3">
-        <v>7040800</v>
+        <v>7216000</v>
       </c>
       <c r="I81" s="3">
-        <v>8440300</v>
+        <v>8650400</v>
       </c>
       <c r="J81" s="3">
-        <v>7153200</v>
+        <v>7331200</v>
       </c>
       <c r="K81" s="3">
         <v>6731300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3440900</v>
+        <v>3526600</v>
       </c>
       <c r="E83" s="3">
-        <v>3225900</v>
+        <v>3306200</v>
       </c>
       <c r="F83" s="3">
-        <v>2978400</v>
+        <v>3052500</v>
       </c>
       <c r="G83" s="3">
-        <v>3036800</v>
+        <v>3112400</v>
       </c>
       <c r="H83" s="3">
-        <v>3243200</v>
+        <v>3323900</v>
       </c>
       <c r="I83" s="3">
-        <v>2620700</v>
+        <v>2685900</v>
       </c>
       <c r="J83" s="3">
-        <v>2802300</v>
+        <v>2872000</v>
       </c>
       <c r="K83" s="3">
         <v>2564900</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5419700</v>
+        <v>5554600</v>
       </c>
       <c r="E89" s="3">
-        <v>29941900</v>
+        <v>30687200</v>
       </c>
       <c r="F89" s="3">
-        <v>61266000</v>
+        <v>62791000</v>
       </c>
       <c r="G89" s="3">
-        <v>71491500</v>
+        <v>73271100</v>
       </c>
       <c r="H89" s="3">
-        <v>3662500</v>
+        <v>3753700</v>
       </c>
       <c r="I89" s="3">
-        <v>3691700</v>
+        <v>3783600</v>
       </c>
       <c r="J89" s="3">
-        <v>43431200</v>
+        <v>44512200</v>
       </c>
       <c r="K89" s="3">
         <v>23678000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12369700</v>
+        <v>-12677600</v>
       </c>
       <c r="E91" s="3">
-        <v>-9797600</v>
+        <v>-10041500</v>
       </c>
       <c r="F91" s="3">
-        <v>-10823200</v>
+        <v>-11092600</v>
       </c>
       <c r="G91" s="3">
-        <v>-7982100</v>
+        <v>-8180700</v>
       </c>
       <c r="H91" s="3">
-        <v>-13796200</v>
+        <v>-14139600</v>
       </c>
       <c r="I91" s="3">
-        <v>-11591600</v>
+        <v>-11880100</v>
       </c>
       <c r="J91" s="3">
-        <v>-8051200</v>
+        <v>-8251600</v>
       </c>
       <c r="K91" s="3">
         <v>-7130600</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5799000</v>
+        <v>-5943400</v>
       </c>
       <c r="E94" s="3">
-        <v>-4212600</v>
+        <v>-4317400</v>
       </c>
       <c r="F94" s="3">
-        <v>-4014800</v>
+        <v>-4114700</v>
       </c>
       <c r="G94" s="3">
-        <v>-7802700</v>
+        <v>-7996900</v>
       </c>
       <c r="H94" s="3">
-        <v>-7812400</v>
+        <v>-8006800</v>
       </c>
       <c r="I94" s="3">
-        <v>3402000</v>
+        <v>3486700</v>
       </c>
       <c r="J94" s="3">
-        <v>-4331400</v>
+        <v>-4439300</v>
       </c>
       <c r="K94" s="3">
         <v>-14933900</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2443500</v>
+        <v>-2504300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1997100</v>
+        <v>-2046800</v>
       </c>
       <c r="F96" s="3">
-        <v>-1419000</v>
+        <v>-1454300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-4077500</v>
+        <v>-4179000</v>
       </c>
       <c r="I96" s="3">
-        <v>-3369600</v>
+        <v>-3453500</v>
       </c>
       <c r="J96" s="3">
-        <v>-2880100</v>
+        <v>-2951800</v>
       </c>
       <c r="K96" s="3">
         <v>-2505300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2545000</v>
+        <v>-2608400</v>
       </c>
       <c r="E100" s="3">
-        <v>-10768100</v>
+        <v>-11036100</v>
       </c>
       <c r="F100" s="3">
-        <v>-1428700</v>
+        <v>-1464200</v>
       </c>
       <c r="G100" s="3">
-        <v>-2063100</v>
+        <v>-2114400</v>
       </c>
       <c r="H100" s="3">
-        <v>-10938800</v>
+        <v>-11211100</v>
       </c>
       <c r="I100" s="3">
-        <v>-3567400</v>
+        <v>-3656200</v>
       </c>
       <c r="J100" s="3">
-        <v>4545400</v>
+        <v>4658600</v>
       </c>
       <c r="K100" s="3">
         <v>-6233300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-348000</v>
+        <v>-356600</v>
       </c>
       <c r="E101" s="3">
-        <v>-1577800</v>
+        <v>-1617100</v>
       </c>
       <c r="F101" s="3">
-        <v>5615300</v>
+        <v>5755100</v>
       </c>
       <c r="G101" s="3">
-        <v>-4595100</v>
+        <v>-4709500</v>
       </c>
       <c r="H101" s="3">
-        <v>1476200</v>
+        <v>1513000</v>
       </c>
       <c r="I101" s="3">
-        <v>-643000</v>
+        <v>-659000</v>
       </c>
       <c r="J101" s="3">
-        <v>-6316700</v>
+        <v>-6473900</v>
       </c>
       <c r="K101" s="3">
         <v>-3917900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2951400</v>
+        <v>-3024900</v>
       </c>
       <c r="E102" s="3">
-        <v>13383400</v>
+        <v>13716500</v>
       </c>
       <c r="F102" s="3">
-        <v>61437800</v>
+        <v>62967100</v>
       </c>
       <c r="G102" s="3">
-        <v>57030700</v>
+        <v>58450300</v>
       </c>
       <c r="H102" s="3">
-        <v>-13612500</v>
+        <v>-13951300</v>
       </c>
       <c r="I102" s="3">
-        <v>2883300</v>
+        <v>2955100</v>
       </c>
       <c r="J102" s="3">
-        <v>37328500</v>
+        <v>38257600</v>
       </c>
       <c r="K102" s="3">
         <v>-1407200</v>

--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>SAN</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>116577100</v>
+        <v>49475000</v>
       </c>
       <c r="E8" s="3">
-        <v>79115900</v>
+        <v>44109200</v>
       </c>
       <c r="F8" s="3">
-        <v>51462400</v>
+        <v>44361400</v>
       </c>
       <c r="G8" s="3">
-        <v>50662700</v>
+        <v>38948000</v>
       </c>
       <c r="H8" s="3">
-        <v>62895100</v>
+        <v>45938700</v>
       </c>
       <c r="I8" s="3">
-        <v>60170400</v>
+        <v>45026300</v>
       </c>
       <c r="J8" s="3">
-        <v>62071000</v>
+        <v>47312700</v>
       </c>
       <c r="K8" s="3">
         <v>59844300</v>
@@ -815,26 +815,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>49475000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>44109200</v>
+      </c>
+      <c r="F10" s="3">
+        <v>44361400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>38948000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>45938700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>45026300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>47312700</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>187900</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>229800</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>854100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>14094200</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>2775200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>152300</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>1374900</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-3526600</v>
+        <v>1415900</v>
       </c>
       <c r="E15" s="3">
-        <v>-3306200</v>
+        <v>1416100</v>
       </c>
       <c r="F15" s="3">
-        <v>-3052500</v>
+        <v>1389700</v>
       </c>
       <c r="G15" s="3">
-        <v>-3112400</v>
+        <v>1604900</v>
       </c>
       <c r="H15" s="3">
-        <v>-3323900</v>
+        <v>1481300</v>
       </c>
       <c r="I15" s="3">
-        <v>-2685900</v>
+        <v>1456400</v>
       </c>
       <c r="J15" s="3">
-        <v>-2872000</v>
+        <v>1540600</v>
       </c>
       <c r="K15" s="3">
         <v>-2564900</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>82962600</v>
+        <v>31094300</v>
       </c>
       <c r="E17" s="3">
-        <v>48365600</v>
+        <v>27581500</v>
       </c>
       <c r="F17" s="3">
-        <v>22684800</v>
+        <v>26963500</v>
       </c>
       <c r="G17" s="3">
-        <v>28919400</v>
+        <v>27393300</v>
       </c>
       <c r="H17" s="3">
-        <v>34160600</v>
+        <v>29087600</v>
       </c>
       <c r="I17" s="3">
-        <v>32086100</v>
+        <v>25838100</v>
       </c>
       <c r="J17" s="3">
-        <v>34320100</v>
+        <v>31419300</v>
       </c>
       <c r="K17" s="3">
         <v>36482000</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>33614600</v>
+        <v>18380700</v>
       </c>
       <c r="E18" s="3">
-        <v>30750300</v>
+        <v>16527700</v>
       </c>
       <c r="F18" s="3">
-        <v>28777700</v>
+        <v>17397900</v>
       </c>
       <c r="G18" s="3">
-        <v>21743300</v>
+        <v>11554700</v>
       </c>
       <c r="H18" s="3">
-        <v>28734500</v>
+        <v>16851100</v>
       </c>
       <c r="I18" s="3">
-        <v>28084300</v>
+        <v>19188200</v>
       </c>
       <c r="J18" s="3">
-        <v>27750900</v>
+        <v>15893400</v>
       </c>
       <c r="K18" s="3">
         <v>23362200</v>
@@ -1184,26 +1184,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-15384600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-13859400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-12665400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-24042700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-14841800</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I20" s="3">
-        <v>-12355300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-14358900</v>
+        <v>2776500</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>-11678900</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21756000</v>
+        <v>19796600</v>
       </c>
       <c r="E21" s="3">
-        <v>20196500</v>
+        <v>17943800</v>
       </c>
       <c r="F21" s="3">
-        <v>19164300</v>
+        <v>18787700</v>
       </c>
       <c r="G21" s="3">
-        <v>812400</v>
+        <v>13159600</v>
       </c>
       <c r="H21" s="3">
-        <v>17215900</v>
+        <v>18332400</v>
       </c>
       <c r="I21" s="3">
-        <v>18414500</v>
+        <v>17868100</v>
       </c>
       <c r="J21" s="3">
-        <v>16263500</v>
+        <v>17434000</v>
       </c>
       <c r="K21" s="3">
         <v>14247300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>18230000</v>
+        <v>18192800</v>
       </c>
       <c r="E23" s="3">
-        <v>16890900</v>
+        <v>16298000</v>
       </c>
       <c r="F23" s="3">
-        <v>16112300</v>
+        <v>16543800</v>
       </c>
       <c r="G23" s="3">
-        <v>-2299400</v>
+        <v>-2539400</v>
       </c>
       <c r="H23" s="3">
-        <v>13892600</v>
+        <v>14075900</v>
       </c>
       <c r="I23" s="3">
-        <v>15729000</v>
+        <v>16259400</v>
       </c>
       <c r="J23" s="3">
-        <v>13392000</v>
+        <v>14518500</v>
       </c>
       <c r="K23" s="3">
         <v>11683300</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4736100</v>
+        <v>4726400</v>
       </c>
       <c r="E24" s="3">
-        <v>4968700</v>
+        <v>4794300</v>
       </c>
       <c r="F24" s="3">
-        <v>5420600</v>
+        <v>5565800</v>
       </c>
       <c r="G24" s="3">
-        <v>6238000</v>
+        <v>6889300</v>
       </c>
       <c r="H24" s="3">
-        <v>4903300</v>
+        <v>4968000</v>
       </c>
       <c r="I24" s="3">
-        <v>5411700</v>
+        <v>5594200</v>
       </c>
       <c r="J24" s="3">
-        <v>4301900</v>
+        <v>4663800</v>
       </c>
       <c r="K24" s="3">
         <v>3561000</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>13493900</v>
+        <v>13466300</v>
       </c>
       <c r="E26" s="3">
-        <v>11922200</v>
+        <v>11503700</v>
       </c>
       <c r="F26" s="3">
-        <v>10691700</v>
+        <v>10978100</v>
       </c>
       <c r="G26" s="3">
-        <v>-8537400</v>
+        <v>-9428700</v>
       </c>
       <c r="H26" s="3">
-        <v>8989300</v>
+        <v>9107800</v>
       </c>
       <c r="I26" s="3">
-        <v>10317300</v>
+        <v>10665200</v>
       </c>
       <c r="J26" s="3">
-        <v>9090100</v>
+        <v>9854700</v>
       </c>
       <c r="K26" s="3">
         <v>8122300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12267800</v>
+        <v>11698900</v>
       </c>
       <c r="E27" s="3">
-        <v>10638500</v>
+        <v>9699700</v>
       </c>
       <c r="F27" s="3">
-        <v>8998100</v>
+        <v>8595500</v>
       </c>
       <c r="G27" s="3">
-        <v>-9714800</v>
+        <v>-11404300</v>
       </c>
       <c r="H27" s="3">
-        <v>7216000</v>
+        <v>6643500</v>
       </c>
       <c r="I27" s="3">
-        <v>8650400</v>
+        <v>8300900</v>
       </c>
       <c r="J27" s="3">
-        <v>7331200</v>
+        <v>7473600</v>
       </c>
       <c r="K27" s="3">
         <v>6731300</v>
@@ -1724,26 +1724,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>15384600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>13859400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>12665400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>24042700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>14841800</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I32" s="3">
-        <v>12355300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>14358900</v>
+        <v>-2776500</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>11678900</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12267800</v>
+        <v>12242700</v>
       </c>
       <c r="E33" s="3">
-        <v>10638500</v>
+        <v>10265000</v>
       </c>
       <c r="F33" s="3">
-        <v>8998100</v>
+        <v>9239200</v>
       </c>
       <c r="G33" s="3">
-        <v>-9714800</v>
+        <v>-10729100</v>
       </c>
       <c r="H33" s="3">
-        <v>7216000</v>
+        <v>7311200</v>
       </c>
       <c r="I33" s="3">
-        <v>8650400</v>
+        <v>8942100</v>
       </c>
       <c r="J33" s="3">
-        <v>7331200</v>
+        <v>7947900</v>
       </c>
       <c r="K33" s="3">
         <v>6731300</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12267800</v>
+        <v>12242700</v>
       </c>
       <c r="E35" s="3">
-        <v>10638500</v>
+        <v>10265000</v>
       </c>
       <c r="F35" s="3">
-        <v>8998100</v>
+        <v>9239200</v>
       </c>
       <c r="G35" s="3">
-        <v>-9714800</v>
+        <v>-10729100</v>
       </c>
       <c r="H35" s="3">
-        <v>7216000</v>
+        <v>7311200</v>
       </c>
       <c r="I35" s="3">
-        <v>8650400</v>
+        <v>8942100</v>
       </c>
       <c r="J35" s="3">
-        <v>7331200</v>
+        <v>7947900</v>
       </c>
       <c r="K35" s="3">
         <v>6731300</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>266294000</v>
+        <v>243552600</v>
       </c>
       <c r="E41" s="3">
-        <v>264105000</v>
+        <v>238402300</v>
       </c>
       <c r="F41" s="3">
-        <v>250701000</v>
+        <v>239609900</v>
       </c>
       <c r="G41" s="3">
-        <v>184236000</v>
+        <v>188182300</v>
       </c>
       <c r="H41" s="3">
-        <v>132404000</v>
+        <v>113418200</v>
       </c>
       <c r="I41" s="3">
-        <v>143173000</v>
+        <v>130138500</v>
       </c>
       <c r="J41" s="3">
-        <v>152044000</v>
+        <v>133279300</v>
       </c>
       <c r="K41" s="3">
         <v>113303000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>314795000</v>
+        <v>256761400</v>
       </c>
       <c r="E42" s="3">
-        <v>238984000</v>
+        <v>220567500</v>
       </c>
       <c r="F42" s="3">
-        <v>161861000</v>
+        <v>192003900</v>
       </c>
       <c r="G42" s="3">
-        <v>164238000</v>
+        <v>252831800</v>
       </c>
       <c r="H42" s="3">
-        <v>175288000</v>
+        <v>248831800</v>
       </c>
       <c r="I42" s="3">
-        <v>180445000</v>
+        <v>199237500</v>
       </c>
       <c r="J42" s="3">
-        <v>154349000</v>
+        <v>230456300</v>
       </c>
       <c r="K42" s="3">
         <v>151565000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>11742000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>9832200</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>6546100</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>6532100</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>7661300</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>11543400</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>8445000</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>3072800</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>3325900</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>4159000</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>4998200</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>5038700</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>6275500</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>16246400</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>266400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>376200</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>498100</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>445300</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>130200</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>105300</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>4459700</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>518612800</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>475713400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>445785300</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>456422000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>378591600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>347300200</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>395679600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8468700</v>
+        <v>216133500</v>
       </c>
       <c r="E47" s="3">
-        <v>8434400</v>
+        <v>177886100</v>
       </c>
       <c r="F47" s="3">
-        <v>8334700</v>
+        <v>172478100</v>
       </c>
       <c r="G47" s="3">
-        <v>8442100</v>
+        <v>186973700</v>
       </c>
       <c r="H47" s="3">
-        <v>9715900</v>
+        <v>188448000</v>
       </c>
       <c r="I47" s="3">
-        <v>8404500</v>
+        <v>204632500</v>
       </c>
       <c r="J47" s="3">
-        <v>6849400</v>
+        <v>210022800</v>
       </c>
       <c r="K47" s="3">
         <v>5247100</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>37527700</v>
+        <v>36394400</v>
       </c>
       <c r="E48" s="3">
-        <v>37739300</v>
+        <v>35314700</v>
       </c>
       <c r="F48" s="3">
-        <v>36906300</v>
+        <v>36781500</v>
       </c>
       <c r="G48" s="3">
-        <v>36257300</v>
+        <v>38864800</v>
       </c>
       <c r="H48" s="3">
-        <v>39026300</v>
+        <v>38449100</v>
       </c>
       <c r="I48" s="3">
-        <v>28971500</v>
+        <v>28158900</v>
       </c>
       <c r="J48" s="3">
-        <v>25446000</v>
+        <v>24795900</v>
       </c>
       <c r="K48" s="3">
         <v>25265300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>22009100</v>
+        <v>21964200</v>
       </c>
       <c r="E49" s="3">
-        <v>20651200</v>
+        <v>19926300</v>
       </c>
       <c r="F49" s="3">
-        <v>18368400</v>
+        <v>18860500</v>
       </c>
       <c r="G49" s="3">
-        <v>17619700</v>
+        <v>19459300</v>
       </c>
       <c r="H49" s="3">
-        <v>30666100</v>
+        <v>31070600</v>
       </c>
       <c r="I49" s="3">
-        <v>31633100</v>
+        <v>32699800</v>
       </c>
       <c r="J49" s="3">
-        <v>31769300</v>
+        <v>34441600</v>
       </c>
       <c r="K49" s="3">
         <v>31921800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27448500</v>
+        <v>7882200</v>
       </c>
       <c r="E52" s="3">
-        <v>28337900</v>
+        <v>8982600</v>
       </c>
       <c r="F52" s="3">
-        <v>28264800</v>
+        <v>8235000</v>
       </c>
       <c r="G52" s="3">
-        <v>26943500</v>
+        <v>11600000</v>
       </c>
       <c r="H52" s="3">
-        <v>31303000</v>
+        <v>9279500</v>
       </c>
       <c r="I52" s="3">
-        <v>32894600</v>
+        <v>9158500</v>
       </c>
       <c r="J52" s="3">
-        <v>43300500</v>
+        <v>9775500</v>
       </c>
       <c r="K52" s="3">
         <v>29899300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1990430000</v>
+        <v>1986362300</v>
       </c>
       <c r="E54" s="3">
-        <v>1921310000</v>
+        <v>1853862300</v>
       </c>
       <c r="F54" s="3">
-        <v>1767550000</v>
+        <v>1814892500</v>
       </c>
       <c r="G54" s="3">
-        <v>1670540000</v>
+        <v>1844954100</v>
       </c>
       <c r="H54" s="3">
-        <v>1686540000</v>
+        <v>1708781300</v>
       </c>
       <c r="I54" s="3">
-        <v>1616290000</v>
+        <v>1670793500</v>
       </c>
       <c r="J54" s="3">
-        <v>1599710000</v>
+        <v>1734275900</v>
       </c>
       <c r="K54" s="3">
         <v>1452950000</v>
@@ -2660,26 +2660,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>168669200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>167599700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>138923000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>167580400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>176567200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>144867200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>144797100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4259800</v>
+        <v>91244600</v>
       </c>
       <c r="E59" s="3">
-        <v>3367100</v>
+        <v>64964200</v>
       </c>
       <c r="F59" s="3">
-        <v>2422300</v>
+        <v>39349500</v>
       </c>
       <c r="G59" s="3">
-        <v>2601800</v>
+        <v>29683200</v>
       </c>
       <c r="H59" s="3">
-        <v>3101300</v>
+        <v>24546100</v>
       </c>
       <c r="I59" s="3">
-        <v>2843200</v>
+        <v>26075100</v>
       </c>
       <c r="J59" s="3">
-        <v>3051400</v>
+        <v>68776400</v>
       </c>
       <c r="K59" s="3">
         <v>2906700</v>
@@ -2795,26 +2795,26 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>341782000</v>
+        <v>239809900</v>
       </c>
       <c r="E61" s="3">
-        <v>310504000</v>
+        <v>214173300</v>
       </c>
       <c r="F61" s="3">
-        <v>272650000</v>
+        <v>212005000</v>
       </c>
       <c r="G61" s="3">
-        <v>260584000</v>
+        <v>211825100</v>
       </c>
       <c r="H61" s="3">
-        <v>290166000</v>
+        <v>201423000</v>
       </c>
       <c r="I61" s="3">
-        <v>273155000</v>
+        <v>208795500</v>
       </c>
       <c r="J61" s="3">
-        <v>241419000</v>
+        <v>196848000</v>
       </c>
       <c r="K61" s="3">
         <v>248323000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>16090100</v>
+        <v>63658700</v>
       </c>
       <c r="E62" s="3">
-        <v>16145500</v>
+        <v>53951100</v>
       </c>
       <c r="F62" s="3">
-        <v>17771400</v>
+        <v>52417800</v>
       </c>
       <c r="G62" s="3">
-        <v>18591100</v>
+        <v>33136400</v>
       </c>
       <c r="H62" s="3">
-        <v>22715800</v>
+        <v>31668700</v>
       </c>
       <c r="I62" s="3">
-        <v>20815100</v>
+        <v>35803800</v>
       </c>
       <c r="J62" s="3">
-        <v>21405500</v>
+        <v>40679600</v>
       </c>
       <c r="K62" s="3">
         <v>21866000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1884740000</v>
+        <v>1871140700</v>
       </c>
       <c r="E66" s="3">
-        <v>1822620000</v>
+        <v>1749571400</v>
       </c>
       <c r="F66" s="3">
-        <v>1671260000</v>
+        <v>1704517200</v>
       </c>
       <c r="G66" s="3">
-        <v>1580290000</v>
+        <v>1733245300</v>
       </c>
       <c r="H66" s="3">
-        <v>1575700000</v>
+        <v>1584598800</v>
       </c>
       <c r="I66" s="3">
-        <v>1509440000</v>
+        <v>1547870400</v>
       </c>
       <c r="J66" s="3">
-        <v>1495060000</v>
+        <v>1605994200</v>
       </c>
       <c r="K66" s="3">
         <v>1354280000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>94356400</v>
+        <v>84424700</v>
       </c>
       <c r="E72" s="3">
-        <v>84517600</v>
+        <v>73015900</v>
       </c>
       <c r="F72" s="3">
-        <v>75756500</v>
+        <v>69955600</v>
       </c>
       <c r="G72" s="3">
-        <v>62925000</v>
+        <v>63256300</v>
       </c>
       <c r="H72" s="3">
-        <v>74810600</v>
+        <v>69084300</v>
       </c>
       <c r="I72" s="3">
-        <v>71513300</v>
+        <v>68438300</v>
       </c>
       <c r="J72" s="3">
-        <v>66518000</v>
+        <v>66882800</v>
       </c>
       <c r="K72" s="3">
         <v>60930300</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>105691000</v>
+        <v>105474700</v>
       </c>
       <c r="E76" s="3">
-        <v>98691600</v>
+        <v>95227100</v>
       </c>
       <c r="F76" s="3">
-        <v>96283700</v>
+        <v>98862700</v>
       </c>
       <c r="G76" s="3">
-        <v>90242800</v>
+        <v>99664800</v>
       </c>
       <c r="H76" s="3">
-        <v>110839000</v>
+        <v>112300500</v>
       </c>
       <c r="I76" s="3">
-        <v>106852000</v>
+        <v>110455700</v>
       </c>
       <c r="J76" s="3">
-        <v>104656000</v>
+        <v>113459400</v>
       </c>
       <c r="K76" s="3">
         <v>98667700</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12267800</v>
+        <v>12242700</v>
       </c>
       <c r="E81" s="3">
-        <v>10638500</v>
+        <v>10265000</v>
       </c>
       <c r="F81" s="3">
-        <v>8998100</v>
+        <v>9239200</v>
       </c>
       <c r="G81" s="3">
-        <v>-9714800</v>
+        <v>-10729100</v>
       </c>
       <c r="H81" s="3">
-        <v>7216000</v>
+        <v>7311200</v>
       </c>
       <c r="I81" s="3">
-        <v>8650400</v>
+        <v>8942100</v>
       </c>
       <c r="J81" s="3">
-        <v>7331200</v>
+        <v>7947900</v>
       </c>
       <c r="K81" s="3">
         <v>6731300</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3526600</v>
+        <v>1939900</v>
       </c>
       <c r="E83" s="3">
-        <v>3306200</v>
+        <v>1960000</v>
       </c>
       <c r="F83" s="3">
-        <v>3052500</v>
+        <v>1982300</v>
       </c>
       <c r="G83" s="3">
-        <v>3112400</v>
+        <v>2341300</v>
       </c>
       <c r="H83" s="3">
-        <v>3323900</v>
+        <v>2283700</v>
       </c>
       <c r="I83" s="3">
-        <v>2685900</v>
+        <v>1341900</v>
       </c>
       <c r="J83" s="3">
-        <v>2872000</v>
+        <v>1428900</v>
       </c>
       <c r="K83" s="3">
         <v>2564900</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>5554600</v>
+        <v>5543300</v>
       </c>
       <c r="E89" s="3">
-        <v>30687200</v>
+        <v>29609900</v>
       </c>
       <c r="F89" s="3">
-        <v>62791000</v>
+        <v>64472900</v>
       </c>
       <c r="G89" s="3">
-        <v>73271100</v>
+        <v>80921100</v>
       </c>
       <c r="H89" s="3">
-        <v>3753700</v>
+        <v>3803200</v>
       </c>
       <c r="I89" s="3">
-        <v>3783600</v>
+        <v>3911200</v>
       </c>
       <c r="J89" s="3">
-        <v>44512200</v>
+        <v>48256500</v>
       </c>
       <c r="K89" s="3">
         <v>23678000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-12677600</v>
+        <v>-12651700</v>
       </c>
       <c r="E91" s="3">
-        <v>-10041500</v>
+        <v>-9689000</v>
       </c>
       <c r="F91" s="3">
-        <v>-11092600</v>
+        <v>-11389700</v>
       </c>
       <c r="G91" s="3">
-        <v>-8180700</v>
+        <v>-9034900</v>
       </c>
       <c r="H91" s="3">
-        <v>-14139600</v>
+        <v>-14326100</v>
       </c>
       <c r="I91" s="3">
-        <v>-11880100</v>
+        <v>-12280700</v>
       </c>
       <c r="J91" s="3">
-        <v>-8251600</v>
+        <v>-8945700</v>
       </c>
       <c r="K91" s="3">
         <v>-7130600</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5943400</v>
+        <v>-5931200</v>
       </c>
       <c r="E94" s="3">
-        <v>-4317400</v>
+        <v>-4165900</v>
       </c>
       <c r="F94" s="3">
-        <v>-4114700</v>
+        <v>-4225000</v>
       </c>
       <c r="G94" s="3">
-        <v>-7996900</v>
+        <v>-8831800</v>
       </c>
       <c r="H94" s="3">
-        <v>-8006800</v>
+        <v>-8112400</v>
       </c>
       <c r="I94" s="3">
-        <v>3486700</v>
+        <v>3604300</v>
       </c>
       <c r="J94" s="3">
-        <v>-4439300</v>
+        <v>-4812700</v>
       </c>
       <c r="K94" s="3">
         <v>-14933900</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2504300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-2046800</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-1454300</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-4179000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-3453500</v>
+        <v>3570000</v>
       </c>
       <c r="J96" s="3">
-        <v>-2951800</v>
+        <v>3200000</v>
       </c>
       <c r="K96" s="3">
         <v>-2505300</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2608400</v>
+        <v>-2274800</v>
       </c>
       <c r="E100" s="3">
-        <v>-11036100</v>
+        <v>-10648700</v>
       </c>
       <c r="F100" s="3">
-        <v>-1464200</v>
+        <v>-1503500</v>
       </c>
       <c r="G100" s="3">
-        <v>-2114400</v>
+        <v>-2335200</v>
       </c>
       <c r="H100" s="3">
-        <v>-11211100</v>
+        <v>-11359000</v>
       </c>
       <c r="I100" s="3">
-        <v>-3656200</v>
+        <v>-3779500</v>
       </c>
       <c r="J100" s="3">
-        <v>4658600</v>
+        <v>5050400</v>
       </c>
       <c r="K100" s="3">
         <v>-6233300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-356600</v>
+        <v>-355900</v>
       </c>
       <c r="E101" s="3">
-        <v>-1617100</v>
+        <v>-1560300</v>
       </c>
       <c r="F101" s="3">
-        <v>5755100</v>
+        <v>5909200</v>
       </c>
       <c r="G101" s="3">
-        <v>-4709500</v>
+        <v>-5201200</v>
       </c>
       <c r="H101" s="3">
-        <v>1513000</v>
+        <v>1532900</v>
       </c>
       <c r="I101" s="3">
-        <v>-659000</v>
+        <v>-681200</v>
       </c>
       <c r="J101" s="3">
-        <v>-6473900</v>
+        <v>-7018500</v>
       </c>
       <c r="K101" s="3">
         <v>-3917900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3024900</v>
+        <v>-3018700</v>
       </c>
       <c r="E102" s="3">
-        <v>13716500</v>
+        <v>13235000</v>
       </c>
       <c r="F102" s="3">
-        <v>62967100</v>
+        <v>64653700</v>
       </c>
       <c r="G102" s="3">
-        <v>58450300</v>
+        <v>64552900</v>
       </c>
       <c r="H102" s="3">
-        <v>-13951300</v>
+        <v>-14135300</v>
       </c>
       <c r="I102" s="3">
-        <v>2955100</v>
+        <v>3054700</v>
       </c>
       <c r="J102" s="3">
-        <v>38257600</v>
+        <v>41475700</v>
       </c>
       <c r="K102" s="3">
         <v>-1407200</v>

--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>SAN</t>
   </si>
@@ -656,117 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>49475000</v>
+        <v>52590300</v>
       </c>
       <c r="E8" s="3">
-        <v>44109200</v>
+        <v>50598000</v>
       </c>
       <c r="F8" s="3">
+        <v>44829500</v>
+      </c>
+      <c r="G8" s="3">
         <v>44361400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38948000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>45938700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45026300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>47312700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>59844300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>58387700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>62397900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>61540900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>56488800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>71154000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,36 +815,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>49475000</v>
+        <v>52590300</v>
       </c>
       <c r="E10" s="3">
-        <v>44109200</v>
+        <v>50598000</v>
       </c>
       <c r="F10" s="3">
+        <v>44829500</v>
+      </c>
+      <c r="G10" s="3">
         <v>44361400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>38948000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45938700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>45026300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>47312700</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,36 +979,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>187900</v>
+        <v>1907000</v>
       </c>
       <c r="E14" s="3">
-        <v>229800</v>
+        <v>1310900</v>
       </c>
       <c r="F14" s="3">
+        <v>950100</v>
+      </c>
+      <c r="G14" s="3">
         <v>854100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14094200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2775200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>152300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1374900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1008,54 +1027,60 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1300300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1415900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1416100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1389700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1604900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1481300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1456400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1540600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-2564900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2468300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2637800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-2860100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2625300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-2462700</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>30984600</v>
+      </c>
+      <c r="E17" s="3">
         <v>31094300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27581500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26963500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>27393300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>29087600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25838100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>31419300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36482000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>35299300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37723700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>43658900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40074800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>48114500</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>18380700</v>
+        <v>21605800</v>
       </c>
       <c r="E18" s="3">
-        <v>16527700</v>
+        <v>19503700</v>
       </c>
       <c r="F18" s="3">
+        <v>17248000</v>
+      </c>
+      <c r="G18" s="3">
         <v>17397900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11554700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16851100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19188200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15893400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23362200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23088500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>24674200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17882000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16414000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23039500</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1199,78 +1232,84 @@
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>2776500</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-11678900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13342900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14259300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9056400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8313000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-13815700</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>19796600</v>
+        <v>22906100</v>
       </c>
       <c r="E21" s="3">
-        <v>17943800</v>
+        <v>20919600</v>
       </c>
       <c r="F21" s="3">
+        <v>18664100</v>
+      </c>
+      <c r="G21" s="3">
         <v>18787700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13159600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>18332400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17868100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17434000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>14247300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12166200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>11674000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>11688100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19698700</v>
+      </c>
+      <c r="E23" s="3">
         <v>18192800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16298000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16543800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2539400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14075900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16259400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14518500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11683300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9745600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10414900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8825600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8101000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9223800</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5469500</v>
+      </c>
+      <c r="E24" s="3">
         <v>4726400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4794300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5565800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6889300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4968000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5594200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4663800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3561000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2259000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2414200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2433100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2233300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2060000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14229200</v>
+      </c>
+      <c r="E26" s="3">
         <v>13466300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11503700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10978100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9428700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>9107800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10665200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9854700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8122300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7486500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8000700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6392500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5867700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7163800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12376000</v>
+      </c>
+      <c r="E27" s="3">
         <v>11698900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9699700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8595500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11404300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6643500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8300900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7473600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6731300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5808400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6207300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5012100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6238800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1620,17 +1680,20 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-17900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-16500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>17600</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1739,78 +1808,84 @@
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2776500</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>11678900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13342900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14259300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9056400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8313000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>13815700</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13017900</v>
+      </c>
+      <c r="E33" s="3">
         <v>12242700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10265000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9239200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10729100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7311200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8942100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7947900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6731300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5808400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6207300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4994100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4584200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6256400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13017900</v>
+      </c>
+      <c r="E35" s="3">
         <v>12242700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10265000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9239200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10729100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7311200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8942100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7947900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6731300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5808400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6207300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4994100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4584200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6256400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,125 +2072,132 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>198993700</v>
+      </c>
+      <c r="E41" s="3">
         <v>243552600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>238402300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>239609900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>188182300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113418200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>130138500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>133279300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113303000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>134322000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>143547000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>159238000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>189156000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>163058000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>310474200</v>
+      </c>
+      <c r="E42" s="3">
         <v>256761400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>220567500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>192003900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>252831800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>248831800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>199237500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>230456300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>151565000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>116234000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>124218000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>114921000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>219900000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>223436000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11829400</v>
+      </c>
+      <c r="E43" s="3">
         <v>11742000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9832200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6546100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6532100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7661300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11543400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8445000</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2121,36 +2213,39 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2719700</v>
+      </c>
+      <c r="E44" s="3">
         <v>3072800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3325900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4159000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4998200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5038700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6275500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16246400</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -2166,36 +2261,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1429800</v>
+      </c>
+      <c r="E45" s="3">
         <v>266400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>376200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>498100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>445300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>130200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>105300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4459700</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>528569200</v>
+      </c>
+      <c r="E46" s="3">
         <v>518612800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>475713400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>445785300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>456422000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>378591600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>347300200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>395679600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>223629800</v>
+      </c>
+      <c r="E47" s="3">
         <v>216133500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>177886100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>172478100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>186973700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>188448000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>204632500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>210022800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5247100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3318600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3546500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10661700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4890500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4877200</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32313900</v>
+      </c>
+      <c r="E48" s="3">
         <v>36394400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>35314700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36781500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38864800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38449100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28158900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24795900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25265300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25846700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27621800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38028400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>15218300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16252600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19938900</v>
+      </c>
+      <c r="E49" s="3">
         <v>21964200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19926300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18860500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19459300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31070600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32699800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>34441600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>31921800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30042100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>32105500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>60412900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>30812100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>32964100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6868200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7882200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8982600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8235000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11600000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9279500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9158500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9775500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>29899300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29070300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31066900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31381100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>29252900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29758400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1901937100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1986362300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1853862300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1814892500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1844954100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1708781300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1670793500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1734275900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1452950000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1368140000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1462100000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1334680000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1394020000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1468450000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2784,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2681,8 +2811,8 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2699,36 +2829,39 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>154030400</v>
+      </c>
+      <c r="E58" s="3">
         <v>168669200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>167599700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>138923000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>167580400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>176567200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>144867200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>144797100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -2744,54 +2877,60 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>109288700</v>
+      </c>
+      <c r="E59" s="3">
         <v>91244600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>64964200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>39349500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29683200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24546100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>26075100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>68776400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2906700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2204900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2356400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5088600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5667900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5987600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2816,8 +2955,8 @@
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>250198800</v>
+      </c>
+      <c r="E61" s="3">
         <v>239809900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>214173300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>212005000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>211825100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>201423000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>208795500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>196848000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>248323000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>230887000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>246744000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>229210000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>246179000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>258666000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>58399400</v>
+      </c>
+      <c r="E62" s="3">
         <v>63658700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>53951100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>52417800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33136400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31668700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>35803800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40679600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21866000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20476200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21882600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>36961400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20588600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>23680400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1790821000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1871140700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1749571400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1704517200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1733245300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1584598800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1547870400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1605994200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1354280000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1278270000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1366060000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1250550000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1315120000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1381050000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>88581600</v>
+      </c>
+      <c r="E72" s="3">
         <v>84424700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>73015900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69955600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>63256300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>69084300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>68438300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66882800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>60930300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52801900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>56428400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>140362000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>42600200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>43125800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102082000</v>
+      </c>
+      <c r="E76" s="3">
         <v>105474700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>95227100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>98862700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>99664800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>112300500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>110455700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>113459400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>98667700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>89871200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>96043700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>84126400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>78902300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>87401900</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13017900</v>
+      </c>
+      <c r="E81" s="3">
         <v>12242700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10265000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9239200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10729100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7311200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8942100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7947900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6731300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5808400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6207300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4994100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4584200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6256400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1667900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1939900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1960000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1982300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2341300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2283700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1341900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1428900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2564900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2468300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>2860100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2462700</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25007800</v>
+      </c>
+      <c r="E89" s="3">
         <v>5543300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29609900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>64472900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>80921100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3803200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3911200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48256500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>23678000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5796100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4297100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-41690000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26498000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>42143300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8793900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12651700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9689000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11389700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9034900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14326100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12280700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8945700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7130600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7823400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7303600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2245300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2372800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3988600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3843000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5931200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4165900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4225000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8831800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8112400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3604300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4812700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14933900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6347300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>809800</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-8226100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4242,32 +4475,35 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>3570000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3200000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2505300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1529200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-991600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-978500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1413100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-4095400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5704500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2274800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10648700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1503500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2335200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11359000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3779500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5050400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-6233300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9146400</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>-2004800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-9520800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5428100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-355900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1560300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5909200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5201200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1532900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-681200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7018500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3917900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-532900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
         <v>-6619800</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-2401600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29127200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3018700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13235000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>64653700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>64552900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14135300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3054700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>41475700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1407200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8062300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8372700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-49504700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24116500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21994900</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SAN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>SAN</t>
   </si>
@@ -656,123 +656,129 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>52590300</v>
+        <v>54991200</v>
       </c>
       <c r="E8" s="3">
-        <v>50598000</v>
+        <v>49497900</v>
       </c>
       <c r="F8" s="3">
+        <v>47818100</v>
+      </c>
+      <c r="G8" s="3">
         <v>44829500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>44361400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38948000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>45938700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>45026300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47312700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>59844300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>58387700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>62397900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>61540900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56488800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>71154000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,39 +824,42 @@
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>52590300</v>
+        <v>54991200</v>
       </c>
       <c r="E10" s="3">
-        <v>50598000</v>
+        <v>49497900</v>
       </c>
       <c r="F10" s="3">
+        <v>47818100</v>
+      </c>
+      <c r="G10" s="3">
         <v>44829500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>44361400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>38948000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>45938700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>45026300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>47312700</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -866,9 +875,12 @@
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,39 +998,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1907000</v>
+        <v>827800</v>
       </c>
       <c r="E14" s="3">
-        <v>1310900</v>
+        <v>1902900</v>
       </c>
       <c r="F14" s="3">
+        <v>1309800</v>
+      </c>
+      <c r="G14" s="3">
         <v>950100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>854100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>14094200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2775200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>152300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1374900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,57 +1049,63 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1300300</v>
+        <v>1242200</v>
       </c>
       <c r="E15" s="3">
-        <v>1415900</v>
+        <v>1214400</v>
       </c>
       <c r="F15" s="3">
+        <v>1339700</v>
+      </c>
+      <c r="G15" s="3">
         <v>1416100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1389700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1604900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1481300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1456400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1540600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-2564900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-2468300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>-2637800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-2860100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-2625300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-2462700</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>30984600</v>
+        <v>32229700</v>
       </c>
       <c r="E17" s="3">
-        <v>31094300</v>
+        <v>29635600</v>
       </c>
       <c r="F17" s="3">
+        <v>29922600</v>
+      </c>
+      <c r="G17" s="3">
         <v>27581500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26963500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27393300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29087600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25838100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>31419300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36482000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>35299300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>37723700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>43658900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40074800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>48114500</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>21605800</v>
+        <v>22761500</v>
       </c>
       <c r="E18" s="3">
-        <v>19503700</v>
+        <v>19862300</v>
       </c>
       <c r="F18" s="3">
+        <v>17895400</v>
+      </c>
+      <c r="G18" s="3">
         <v>17248000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17397900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11554700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16851100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19188200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15893400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23362200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23088500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>24674200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17882000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16414000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>23039500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1244,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1235,81 +1268,87 @@
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>2776500</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-11678900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13342900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14259300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9056400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8313000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-13815700</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22906100</v>
+        <v>24003800</v>
       </c>
       <c r="E21" s="3">
-        <v>20919600</v>
+        <v>21076700</v>
       </c>
       <c r="F21" s="3">
+        <v>19235100</v>
+      </c>
+      <c r="G21" s="3">
         <v>18664100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>18787700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13159600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18332400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17868100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17434000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>14247300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12166200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>11674000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>11688100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1337,8 +1376,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1355,105 +1394,114 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>19698700</v>
+        <v>21933800</v>
       </c>
       <c r="E23" s="3">
-        <v>18192800</v>
+        <v>17959400</v>
       </c>
       <c r="F23" s="3">
+        <v>16585600</v>
+      </c>
+      <c r="G23" s="3">
         <v>16298000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>16543800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2539400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14075900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16259400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14518500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11683300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9745600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10414900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8825600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8101000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9223800</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>5469500</v>
+        <v>5545400</v>
       </c>
       <c r="E24" s="3">
-        <v>4726400</v>
+        <v>5015000</v>
       </c>
       <c r="F24" s="3">
+        <v>4288700</v>
+      </c>
+      <c r="G24" s="3">
         <v>4794300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5565800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6889300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4968000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5594200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4663800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3561000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2259000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2414200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2433100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2233300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2060000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>14229200</v>
+        <v>16388400</v>
       </c>
       <c r="E26" s="3">
-        <v>13466300</v>
+        <v>12944400</v>
       </c>
       <c r="F26" s="3">
+        <v>12296900</v>
+      </c>
+      <c r="G26" s="3">
         <v>11503700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10978100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9428700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9107800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10665200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9854700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8122300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7486500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8000700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6392500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5867700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7163800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15826000</v>
+      </c>
+      <c r="E27" s="3">
         <v>12376000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11698900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9699700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8595500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11404300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6643500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8300900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7473600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6731300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5808400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6207300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5012100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4600600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6238800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,20 +1700,23 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>1810500</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>1284800</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>1169400</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1683,17 +1743,20 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-17900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>17600</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,9 +1853,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1811,81 +1880,87 @@
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2776500</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>11678900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13342900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14259300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9056400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8313000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>13815700</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16556300</v>
+      </c>
+      <c r="E33" s="3">
         <v>13017900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12242700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10265000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9239200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10729100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7311200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8942100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7947900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6731300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5808400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6207300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4994100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4584200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6256400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16556300</v>
+      </c>
+      <c r="E35" s="3">
         <v>13017900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12242700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10265000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9239200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10729100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7311200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8942100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7947900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6731300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5808400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6207300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4994100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4584200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6256400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,134 +2158,141 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>178796500</v>
+      </c>
+      <c r="E41" s="3">
         <v>198993700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>243552600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>238402300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>239609900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>188182300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113418200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>130138500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133279300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>113303000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>134322000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>143547000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>159238000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>189156000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>163058000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>310474200</v>
+        <v>306975500</v>
       </c>
       <c r="E42" s="3">
-        <v>256761400</v>
+        <v>248720400</v>
       </c>
       <c r="F42" s="3">
-        <v>220567500</v>
+        <v>207923100</v>
       </c>
       <c r="G42" s="3">
+        <v>178353100</v>
+      </c>
+      <c r="H42" s="3">
         <v>192003900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>252831800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>248831800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>199237500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>230456300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>151565000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>116234000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>124218000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>114921000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>219900000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>223436000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13070300</v>
+      </c>
+      <c r="E43" s="3">
         <v>11829400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11742000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9832200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6546100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6532100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7661300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11543400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8445000</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2216,39 +2308,42 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2928300</v>
+      </c>
+      <c r="E44" s="3">
         <v>2719700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3072800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3325900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4159000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4998200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5038700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6275500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16246400</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -2264,39 +2359,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>85152000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1429800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>266400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>376200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>498100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>445300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>130200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>105300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4459700</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2312,39 +2410,42 @@
       <c r="Q45" s="3">
         <v>0</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>528569200</v>
+        <v>590587100</v>
       </c>
       <c r="E46" s="3">
-        <v>518612800</v>
+        <v>466815400</v>
       </c>
       <c r="F46" s="3">
-        <v>475713400</v>
+        <v>469774500</v>
       </c>
       <c r="G46" s="3">
+        <v>433499000</v>
+      </c>
+      <c r="H46" s="3">
         <v>445785300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>456422000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>378591600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>347300200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>395679600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2360,153 +2461,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>256319100</v>
+      </c>
+      <c r="E47" s="3">
         <v>223629800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>216133500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>177886100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>172478100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>186973700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>188448000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>204632500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>210022800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5247100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3318600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3546500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10661700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4890500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4877200</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31015600</v>
+      </c>
+      <c r="E48" s="3">
         <v>32313900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36394400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>35314700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36781500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>38864800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38449100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28158900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24795900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25265300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25846700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27621800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38028400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>15218300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16252600</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20321700</v>
+      </c>
+      <c r="E49" s="3">
         <v>19938900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21964200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>19926300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18860500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19459300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>31070600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>32699800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>34441600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>31921800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30042100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>32105500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>60412900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>30812100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>32964100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8026300</v>
+      </c>
+      <c r="E52" s="3">
         <v>6868200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7882200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8982600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8235000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11600000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9279500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9158500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9775500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>29899300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29070300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31066900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>31381100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>29252900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29758400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2192691100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1901937100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1986362300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1853862300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1814892500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1844954100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1708781300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1670793500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1734275900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1452950000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1368140000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1462100000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1334680000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1394020000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1468450000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,8 +2914,9 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2814,8 +2944,8 @@
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -2832,39 +2962,42 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>172125200</v>
+      </c>
+      <c r="E58" s="3">
         <v>154030400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>168669200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>167599700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>138923000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>167580400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>176567200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>144867200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>144797100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2880,57 +3013,63 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>109288700</v>
+        <v>228487700</v>
       </c>
       <c r="E59" s="3">
-        <v>91244600</v>
+        <v>109762900</v>
       </c>
       <c r="F59" s="3">
+        <v>91920000</v>
+      </c>
+      <c r="G59" s="3">
         <v>64964200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39349500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29683200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24546100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26075100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68776400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2906700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2204900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2356400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5088600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5667900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5987600</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2958,8 +3097,8 @@
       <c r="K60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -2976,105 +3115,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>277271300</v>
+      </c>
+      <c r="E61" s="3">
         <v>250198800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>239809900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>214173300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>212005000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>211825100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>201423000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>208795500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>196848000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>248323000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>230887000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>246744000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>229210000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>246179000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>258666000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>58399400</v>
+        <v>64395900</v>
       </c>
       <c r="E62" s="3">
-        <v>63658700</v>
+        <v>59985500</v>
       </c>
       <c r="F62" s="3">
+        <v>65160800</v>
+      </c>
+      <c r="G62" s="3">
         <v>53951100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>52417800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33136400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>31668700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>35803800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40679600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>21866000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20476200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>21882600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>36961400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20588600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>23680400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2060311100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1790821000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1871140700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1749571400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1704517200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1733245300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1584598800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1547870400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1605994200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1354280000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1278270000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1366060000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1250550000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1315120000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1381050000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>111761200</v>
+      </c>
+      <c r="E72" s="3">
         <v>88581600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>84424700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>73015900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69955600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>63256300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>69084300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>68438300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66882800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60930300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52801900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56428400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>140362000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>42600200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43125800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>121134200</v>
+      </c>
+      <c r="E76" s="3">
         <v>102082000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>105474700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>95227100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>98862700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>99664800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>112300500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>110455700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>113459400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>98667700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89871200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>96043700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>84126400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>78902300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>87401900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16556300</v>
+      </c>
+      <c r="E81" s="3">
         <v>13017900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12242700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10265000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9239200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10729100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7311200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8942100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7947900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6731300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5808400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6207300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4994100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4584200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6256400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1667900</v>
+        <v>1562800</v>
       </c>
       <c r="E83" s="3">
-        <v>1939900</v>
+        <v>1607800</v>
       </c>
       <c r="F83" s="3">
+        <v>1879100</v>
+      </c>
+      <c r="G83" s="3">
         <v>1960000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1982300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2341300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2283700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1341900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1428900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2564900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2468300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>2860100</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>2462700</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17418100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25007800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5543300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>29609900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>64472900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>80921100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3803200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3911200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>48256500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23678000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5796100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4297100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-41690000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26498000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42143300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6873300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8793900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12651700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9689000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11389700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9034900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14326100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12280700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8945700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7130600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7823400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7303600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2245300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2372800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3988600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>627000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3843000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5931200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4165900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4225000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8831800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8112400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3604300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4812700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14933900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6347300</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>809800</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-8226100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4478,32 +4711,35 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>3570000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>3200000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2505300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1529200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-991600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-978500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1413100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4095400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16676100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5704500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2274800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10648700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1503500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2335200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11359000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3779500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5050400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6233300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9146400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2004800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-9520800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-10459100</v>
+      </c>
+      <c r="E101" s="3">
         <v>5428100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-355900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1560300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5909200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5201200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1532900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-681200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7018500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3917900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-532900</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-6619800</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-2401600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43926300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29127200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3018700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13235000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>64653700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>64552900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14135300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3054700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>41475700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1407200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8062300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8372700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-49504700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>24116500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>21994900</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
